--- a/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA73A445-1F7E-433C-8181-391225E8C9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD01552F-556F-484C-988F-998C97C0B476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="589">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1824,12 +1824,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ OST_Materials ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ IfcMaterial ] </t>
-  </si>
-  <si>
     <t>[ - ]</t>
   </si>
   <si>
@@ -1845,16 +1839,25 @@
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
-    <t>[ IfcProperty ]</t>
-  </si>
-  <si>
     <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
   </si>
   <si>
     <t>[ IfcAnnotation ]</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_MaterialTags ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial : IfcText : IfcLabel : IfcMaterialRelationship ]</t>
+  </si>
+  <si>
+    <t>[ BuiltInParameter ]</t>
+  </si>
+  <si>
+    <t>[ IfcProperty : IfcIdentifier : IfcText ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
   </si>
 </sst>
 </file>
@@ -2460,7 +2463,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="75">
+  <dxfs count="76">
     <dxf>
       <font>
         <b val="0"/>
@@ -2588,6 +2591,13 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -4611,33 +4621,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="74" headerRowBorderDxfId="73" tableBorderDxfId="72" totalsRowBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="75" headerRowBorderDxfId="74" tableBorderDxfId="73" totalsRowBorderDxfId="72">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="70" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="26" dataDxfId="25"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="24" dataDxfId="23"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="22" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="23" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4962,14 +4972,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B000FC7-022F-4B0D-BBFB-289DF5E27855}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4980,7 +4990,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>177</v>
       </c>
@@ -4991,7 +5001,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>178</v>
       </c>
@@ -5002,7 +5012,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5013,7 +5023,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -5025,7 +5035,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5037,7 +5047,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -5048,7 +5058,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="43" t="s">
         <v>9</v>
       </c>
@@ -5059,7 +5069,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>179</v>
       </c>
@@ -5070,7 +5080,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>181</v>
       </c>
@@ -5081,7 +5091,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>182</v>
       </c>
@@ -5092,7 +5102,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5103,7 +5113,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>183</v>
       </c>
@@ -5114,7 +5124,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>184</v>
       </c>
@@ -5125,7 +5135,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>185</v>
       </c>
@@ -5136,7 +5146,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>186</v>
       </c>
@@ -5147,7 +5157,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -5158,19 +5168,19 @@
         <v>432</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>187</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46244.495308333331</v>
+        <v>46249.322544444447</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>443</v>
       </c>
@@ -5181,7 +5191,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="43" t="s">
         <v>436</v>
       </c>
@@ -5193,7 +5203,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="43" t="s">
         <v>444</v>
       </c>
@@ -5205,7 +5215,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>176</v>
       </c>
@@ -5216,7 +5226,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>188</v>
       </c>
@@ -5227,7 +5237,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>195</v>
       </c>
@@ -5238,7 +5248,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>197</v>
       </c>
@@ -5249,7 +5259,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="43" t="s">
         <v>428</v>
       </c>
@@ -5260,7 +5270,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="43" t="s">
         <v>548</v>
       </c>
@@ -5271,7 +5281,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="43" t="s">
         <v>550</v>
       </c>
@@ -5282,7 +5292,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="43" t="s">
         <v>552</v>
       </c>
@@ -5293,7 +5303,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="43" t="s">
         <v>554</v>
       </c>
@@ -5304,7 +5314,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="43" t="s">
         <v>556</v>
       </c>
@@ -5315,7 +5325,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="43" t="s">
         <v>558</v>
       </c>
@@ -5326,7 +5336,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="43" t="s">
         <v>560</v>
       </c>
@@ -5337,7 +5347,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="43" t="s">
         <v>562</v>
       </c>
@@ -5348,7 +5358,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="43" t="s">
         <v>564</v>
       </c>
@@ -5359,7 +5369,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="43" t="s">
         <v>566</v>
       </c>
@@ -5370,7 +5380,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="43" t="s">
         <v>568</v>
       </c>
@@ -5381,7 +5391,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>570</v>
       </c>
@@ -5392,7 +5402,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="74" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="74" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="43" t="s">
         <v>572</v>
       </c>
@@ -5419,34 +5429,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75533AB-3BC5-4EED-85BC-780B8F4A6EA8}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA22"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6" style="33" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.83203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="45.6640625" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.09765625" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.8984375" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.3984375" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="62.296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.796875" style="33" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="45.69921875" customWidth="1"/>
+    <col min="25" max="25" width="36.09765625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="57" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>374</v>
       </c>
@@ -5529,7 +5539,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -5608,10 +5618,10 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="X2" s="42" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="Y2" s="42" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="Z2" s="42" t="s">
         <v>446</v>
@@ -5620,7 +5630,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -5699,10 +5709,10 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="X3" s="42" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="Y3" s="42" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="Z3" s="42" t="s">
         <v>447</v>
@@ -5711,7 +5721,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -5790,10 +5800,10 @@
         <v>Key-ABNT-4</v>
       </c>
       <c r="X4" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Y4" s="42" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="Z4" s="42" t="s">
         <v>448</v>
@@ -5802,7 +5812,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -5881,10 +5891,10 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="X5" s="42" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Y5" s="42" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z5" s="42" t="s">
         <v>369</v>
@@ -5893,7 +5903,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -5972,10 +5982,10 @@
         <v>Key-ABNT-6</v>
       </c>
       <c r="X6" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Y6" s="42" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="Z6" s="42" t="s">
         <v>449</v>
@@ -5984,7 +5994,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -6063,10 +6073,10 @@
         <v>Key-ABNT-7</v>
       </c>
       <c r="X7" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Y7" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Z7" s="42" t="s">
         <v>450</v>
@@ -6075,7 +6085,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -6154,10 +6164,10 @@
         <v>Key-ABNT-8</v>
       </c>
       <c r="X8" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Y8" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Z8" s="42" t="s">
         <v>451</v>
@@ -6166,7 +6176,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -6245,10 +6255,10 @@
         <v>Key-ABNT-9</v>
       </c>
       <c r="X9" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Y9" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Z9" s="42" t="s">
         <v>452</v>
@@ -6257,7 +6267,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -6336,10 +6346,10 @@
         <v>Key-ABNT-10</v>
       </c>
       <c r="X10" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Y10" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Z10" s="42" t="s">
         <v>453</v>
@@ -6348,7 +6358,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -6427,10 +6437,10 @@
         <v>Key-ABNT-11</v>
       </c>
       <c r="X11" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Y11" s="42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Z11" s="42" t="s">
         <v>454</v>
@@ -6439,7 +6449,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -6518,10 +6528,10 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="X12" s="42" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Y12" s="42" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="Z12" s="42" t="s">
         <v>455</v>
@@ -6530,7 +6540,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -6609,10 +6619,10 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="X13" s="42" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Y13" s="42" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="Z13" s="42" t="s">
         <v>456</v>
@@ -6621,7 +6631,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -6700,10 +6710,10 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="X14" s="75" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="Y14" s="76" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="Z14" s="42" t="s">
         <v>457</v>
@@ -6712,7 +6722,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -6792,10 +6802,10 @@
         <v>Key-ABNT-15</v>
       </c>
       <c r="X15" s="42" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Y15" s="42" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z15" s="61" t="s">
         <v>496</v>
@@ -6805,7 +6815,7 @@
         <v>Programming Phase</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -6885,10 +6895,10 @@
         <v>Key-ABNT-16</v>
       </c>
       <c r="X16" s="42" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Y16" s="42" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z16" s="61" t="s">
         <v>497</v>
@@ -6898,7 +6908,7 @@
         <v>Preliminary Studies Phase</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -6978,10 +6988,10 @@
         <v>Key-ABNT-17</v>
       </c>
       <c r="X17" s="42" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Y17" s="42" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z17" s="61" t="s">
         <v>498</v>
@@ -6991,7 +7001,7 @@
         <v>Project Phase</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -7071,10 +7081,10 @@
         <v>Key-ABNT-18</v>
       </c>
       <c r="X18" s="42" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Y18" s="42" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z18" s="61" t="s">
         <v>499</v>
@@ -7084,7 +7094,7 @@
         <v>Bidding Phase</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -7164,10 +7174,10 @@
         <v>Key-ABNT-19</v>
       </c>
       <c r="X19" s="42" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Y19" s="42" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z19" s="61" t="s">
         <v>503</v>
@@ -7177,7 +7187,7 @@
         <v>Construction Phase</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="57">
         <v>20</v>
       </c>
@@ -7257,10 +7267,10 @@
         <v>Key-ABNT-20</v>
       </c>
       <c r="X20" s="42" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Y20" s="42" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z20" s="61" t="s">
         <v>500</v>
@@ -7270,7 +7280,7 @@
         <v>Commissioning Phase</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="57">
         <v>21</v>
       </c>
@@ -7350,10 +7360,10 @@
         <v>Key-ABNT-21</v>
       </c>
       <c r="X21" s="42" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Y21" s="42" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z21" s="61" t="s">
         <v>501</v>
@@ -7363,7 +7373,7 @@
         <v>Operation Phase</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="57">
         <v>22</v>
       </c>
@@ -7443,10 +7453,10 @@
         <v>Key-ABNT-22</v>
       </c>
       <c r="X22" s="42" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Y22" s="42" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z22" s="61" t="s">
         <v>502</v>
@@ -7458,20 +7468,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y2">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA22 A2:B22">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -7479,13 +7497,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A4D5B2-E607-43E1-969D-E9BC12588F0D}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>375</v>
       </c>
@@ -7550,7 +7568,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -7632,13 +7650,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50BE4DF8-DB25-47BD-BFAE-132A16409236}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.83203125" customWidth="1"/>
+    <col min="2" max="3" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -7649,7 +7667,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -7674,34 +7692,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y169"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.19921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.5" style="38" customWidth="1"/>
     <col min="7" max="7" width="9" style="38" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4" style="38" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" style="38" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.5" style="38" customWidth="1"/>
-    <col min="11" max="11" width="7.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.19921875" style="38" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.1640625" style="38" customWidth="1"/>
-    <col min="14" max="14" width="5.6640625" style="38" customWidth="1"/>
+    <col min="13" max="13" width="20.19921875" style="38" customWidth="1"/>
+    <col min="14" max="14" width="5.69921875" style="38" customWidth="1"/>
     <col min="15" max="15" width="36" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="8.83203125" style="38" customWidth="1"/>
+    <col min="16" max="19" width="8.796875" style="38" customWidth="1"/>
     <col min="20" max="20" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>189</v>
       </c>
@@ -7778,7 +7796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -7855,7 +7873,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -7932,7 +7950,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -8009,7 +8027,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -8086,7 +8104,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -8163,7 +8181,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -8240,7 +8258,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -8317,7 +8335,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -8394,7 +8412,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -8471,7 +8489,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -8548,7 +8566,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -8625,7 +8643,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -8702,7 +8720,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -8779,7 +8797,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -8856,7 +8874,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>16</v>
       </c>
@@ -8933,7 +8951,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>17</v>
       </c>
@@ -9010,7 +9028,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>18</v>
       </c>
@@ -9087,7 +9105,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>19</v>
       </c>
@@ -9164,7 +9182,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>20</v>
       </c>
@@ -9241,7 +9259,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>21</v>
       </c>
@@ -9318,7 +9336,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>22</v>
       </c>
@@ -9395,7 +9413,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>23</v>
       </c>
@@ -9472,7 +9490,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>24</v>
       </c>
@@ -9549,7 +9567,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>25</v>
       </c>
@@ -9626,7 +9644,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>26</v>
       </c>
@@ -9703,7 +9721,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>27</v>
       </c>
@@ -9780,7 +9798,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>28</v>
       </c>
@@ -9857,7 +9875,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>29</v>
       </c>
@@ -9934,7 +9952,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>30</v>
       </c>
@@ -10011,7 +10029,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>31</v>
       </c>
@@ -10088,7 +10106,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>32</v>
       </c>
@@ -10165,7 +10183,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>33</v>
       </c>
@@ -10242,7 +10260,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>34</v>
       </c>
@@ -10319,7 +10337,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>35</v>
       </c>
@@ -10396,7 +10414,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>36</v>
       </c>
@@ -10473,7 +10491,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>37</v>
       </c>
@@ -10550,7 +10568,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>38</v>
       </c>
@@ -10627,7 +10645,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>39</v>
       </c>
@@ -10704,7 +10722,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>40</v>
       </c>
@@ -10781,7 +10799,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>41</v>
       </c>
@@ -10858,7 +10876,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>42</v>
       </c>
@@ -10935,7 +10953,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>43</v>
       </c>
@@ -11012,7 +11030,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>44</v>
       </c>
@@ -11089,7 +11107,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>45</v>
       </c>
@@ -11166,7 +11184,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>46</v>
       </c>
@@ -11243,7 +11261,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>47</v>
       </c>
@@ -11320,7 +11338,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>48</v>
       </c>
@@ -11397,7 +11415,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>49</v>
       </c>
@@ -11474,7 +11492,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>50</v>
       </c>
@@ -11551,7 +11569,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>51</v>
       </c>
@@ -11628,7 +11646,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>52</v>
       </c>
@@ -11705,7 +11723,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>53</v>
       </c>
@@ -11782,7 +11800,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>54</v>
       </c>
@@ -11859,7 +11877,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>55</v>
       </c>
@@ -11936,7 +11954,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>56</v>
       </c>
@@ -12013,7 +12031,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>57</v>
       </c>
@@ -12090,7 +12108,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>58</v>
       </c>
@@ -12167,7 +12185,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>59</v>
       </c>
@@ -12244,7 +12262,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>60</v>
       </c>
@@ -12321,7 +12339,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>61</v>
       </c>
@@ -12398,7 +12416,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>62</v>
       </c>
@@ -12475,7 +12493,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>63</v>
       </c>
@@ -12552,7 +12570,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <v>64</v>
       </c>
@@ -12629,7 +12647,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>65</v>
       </c>
@@ -12706,7 +12724,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>66</v>
       </c>
@@ -12783,7 +12801,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <v>67</v>
       </c>
@@ -12860,7 +12878,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>68</v>
       </c>
@@ -12937,7 +12955,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>69</v>
       </c>
@@ -13014,7 +13032,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>70</v>
       </c>
@@ -13091,7 +13109,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>71</v>
       </c>
@@ -13168,7 +13186,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>72</v>
       </c>
@@ -13245,7 +13263,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>73</v>
       </c>
@@ -13322,7 +13340,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>74</v>
       </c>
@@ -13399,7 +13417,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>75</v>
       </c>
@@ -13476,7 +13494,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>76</v>
       </c>
@@ -13553,7 +13571,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>77</v>
       </c>
@@ -13630,7 +13648,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>78</v>
       </c>
@@ -13707,7 +13725,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>79</v>
       </c>
@@ -13784,7 +13802,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <v>80</v>
       </c>
@@ -13861,7 +13879,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>81</v>
       </c>
@@ -13938,7 +13956,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <v>82</v>
       </c>
@@ -14015,7 +14033,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <v>83</v>
       </c>
@@ -14092,7 +14110,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>84</v>
       </c>
@@ -14169,7 +14187,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>85</v>
       </c>
@@ -14246,7 +14264,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>86</v>
       </c>
@@ -14323,7 +14341,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>87</v>
       </c>
@@ -14400,7 +14418,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>88</v>
       </c>
@@ -14477,7 +14495,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>89</v>
       </c>
@@ -14554,7 +14572,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>90</v>
       </c>
@@ -14631,7 +14649,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>91</v>
       </c>
@@ -14708,7 +14726,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
         <v>92</v>
       </c>
@@ -14785,7 +14803,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <v>93</v>
       </c>
@@ -14862,7 +14880,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
         <v>94</v>
       </c>
@@ -14939,7 +14957,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
         <v>95</v>
       </c>
@@ -15016,7 +15034,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
         <v>96</v>
       </c>
@@ -15093,7 +15111,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
         <v>97</v>
       </c>
@@ -15170,7 +15188,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
         <v>98</v>
       </c>
@@ -15247,7 +15265,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
         <v>99</v>
       </c>
@@ -15324,7 +15342,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
         <v>100</v>
       </c>
@@ -15401,7 +15419,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
         <v>101</v>
       </c>
@@ -15478,7 +15496,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
         <v>102</v>
       </c>
@@ -15555,7 +15573,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
         <v>103</v>
       </c>
@@ -15632,7 +15650,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
         <v>104</v>
       </c>
@@ -15709,7 +15727,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
         <v>105</v>
       </c>
@@ -15786,7 +15804,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
         <v>106</v>
       </c>
@@ -15863,7 +15881,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
         <v>107</v>
       </c>
@@ -15940,7 +15958,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
         <v>108</v>
       </c>
@@ -16017,7 +16035,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
         <v>109</v>
       </c>
@@ -16094,7 +16112,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
         <v>110</v>
       </c>
@@ -16171,7 +16189,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
         <v>111</v>
       </c>
@@ -16248,7 +16266,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8">
         <v>112</v>
       </c>
@@ -16325,7 +16343,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
         <v>113</v>
       </c>
@@ -16402,7 +16420,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8">
         <v>114</v>
       </c>
@@ -16479,7 +16497,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
         <v>115</v>
       </c>
@@ -16556,7 +16574,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="8">
         <v>116</v>
       </c>
@@ -16633,7 +16651,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
         <v>117</v>
       </c>
@@ -16710,7 +16728,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
         <v>118</v>
       </c>
@@ -16787,7 +16805,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
         <v>119</v>
       </c>
@@ -16864,7 +16882,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <v>120</v>
       </c>
@@ -16941,7 +16959,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
         <v>121</v>
       </c>
@@ -17018,7 +17036,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
         <v>122</v>
       </c>
@@ -17095,7 +17113,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
         <v>123</v>
       </c>
@@ -17172,7 +17190,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
         <v>124</v>
       </c>
@@ -17249,7 +17267,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
         <v>125</v>
       </c>
@@ -17326,7 +17344,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="8">
         <v>126</v>
       </c>
@@ -17403,7 +17421,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <v>127</v>
       </c>
@@ -17480,7 +17498,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
         <v>128</v>
       </c>
@@ -17557,7 +17575,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <v>129</v>
       </c>
@@ -17634,7 +17652,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="8">
         <v>130</v>
       </c>
@@ -17711,7 +17729,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <v>131</v>
       </c>
@@ -17788,7 +17806,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
         <v>132</v>
       </c>
@@ -17865,7 +17883,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <v>133</v>
       </c>
@@ -17942,7 +17960,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
         <v>134</v>
       </c>
@@ -18019,7 +18037,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <v>135</v>
       </c>
@@ -18096,7 +18114,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
         <v>136</v>
       </c>
@@ -18173,7 +18191,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <v>137</v>
       </c>
@@ -18250,7 +18268,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
         <v>138</v>
       </c>
@@ -18327,7 +18345,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <v>139</v>
       </c>
@@ -18404,7 +18422,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
         <v>140</v>
       </c>
@@ -18481,7 +18499,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <v>141</v>
       </c>
@@ -18558,7 +18576,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
         <v>142</v>
       </c>
@@ -18635,7 +18653,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <v>143</v>
       </c>
@@ -18712,7 +18730,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
         <v>144</v>
       </c>
@@ -18789,7 +18807,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <v>145</v>
       </c>
@@ -18866,7 +18884,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
         <v>146</v>
       </c>
@@ -18943,7 +18961,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <v>147</v>
       </c>
@@ -19020,7 +19038,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
         <v>148</v>
       </c>
@@ -19097,7 +19115,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <v>149</v>
       </c>
@@ -19174,7 +19192,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
         <v>150</v>
       </c>
@@ -19251,7 +19269,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <v>151</v>
       </c>
@@ -19328,7 +19346,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
         <v>152</v>
       </c>
@@ -19405,7 +19423,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <v>153</v>
       </c>
@@ -19482,7 +19500,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
         <v>154</v>
       </c>
@@ -19559,7 +19577,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
         <v>155</v>
       </c>
@@ -19636,7 +19654,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
         <v>156</v>
       </c>
@@ -19713,7 +19731,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
         <v>157</v>
       </c>
@@ -19790,7 +19808,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
         <v>158</v>
       </c>
@@ -19867,7 +19885,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
         <v>159</v>
       </c>
@@ -19944,7 +19962,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
         <v>160</v>
       </c>
@@ -20021,7 +20039,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
         <v>161</v>
       </c>
@@ -20098,7 +20116,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
         <v>162</v>
       </c>
@@ -20175,7 +20193,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
         <v>163</v>
       </c>
@@ -20252,7 +20270,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
         <v>164</v>
       </c>
@@ -20329,7 +20347,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <v>165</v>
       </c>
@@ -20406,7 +20424,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <v>166</v>
       </c>
@@ -20483,7 +20501,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <v>167</v>
       </c>
@@ -20560,7 +20578,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
         <v>168</v>
       </c>
@@ -20637,7 +20655,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
         <v>169</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD01552F-556F-484C-988F-998C97C0B476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984F061A-BDC3-423C-992F-EAEC4EE83BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4663" uniqueCount="607">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1858,6 +1858,60 @@
   </si>
   <si>
     <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
+  </si>
+  <si>
+    <t>Programming Phase</t>
+  </si>
+  <si>
+    <t>Preliminary Studies Phase</t>
+  </si>
+  <si>
+    <t>Project Phase</t>
+  </si>
+  <si>
+    <t>Bidding Phase</t>
+  </si>
+  <si>
+    <t>Construction Phase</t>
+  </si>
+  <si>
+    <t>Commissioning Phase</t>
+  </si>
+  <si>
+    <t>Operation Phase</t>
+  </si>
+  <si>
+    <t>Closure and Demolition Phase</t>
+  </si>
+  <si>
+    <t>Fase de programación</t>
+  </si>
+  <si>
+    <t>Fase de Estudios Preliminares</t>
+  </si>
+  <si>
+    <t>Fase del proyecto</t>
+  </si>
+  <si>
+    <t>Fase de subasta</t>
+  </si>
+  <si>
+    <t>Fase de construcción</t>
+  </si>
+  <si>
+    <t>Fase de puesta en servicio</t>
+  </si>
+  <si>
+    <t>Fase de Operación</t>
+  </si>
+  <si>
+    <t>Fase de cierre y demolición</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo Ifc</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2517,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="76">
+  <dxfs count="77">
     <dxf>
       <font>
         <b val="0"/>
@@ -2584,6 +2638,14 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -4621,33 +4683,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="75" headerRowBorderDxfId="74" tableBorderDxfId="73" totalsRowBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="76" headerRowBorderDxfId="75" tableBorderDxfId="74" totalsRowBorderDxfId="73">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="71" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="72" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="70" dataDxfId="69"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="68" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="66" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="24" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4972,14 +5034,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B000FC7-022F-4B0D-BBFB-289DF5E27855}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4990,7 +5052,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>177</v>
       </c>
@@ -5001,7 +5063,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>178</v>
       </c>
@@ -5012,7 +5074,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5023,7 +5085,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -5035,7 +5097,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5047,7 +5109,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -5058,7 +5120,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="43" t="s">
         <v>9</v>
       </c>
@@ -5069,7 +5131,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>179</v>
       </c>
@@ -5080,7 +5142,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>181</v>
       </c>
@@ -5091,7 +5153,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>182</v>
       </c>
@@ -5102,7 +5164,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5113,7 +5175,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>183</v>
       </c>
@@ -5124,7 +5186,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>184</v>
       </c>
@@ -5135,7 +5197,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>185</v>
       </c>
@@ -5146,7 +5208,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>186</v>
       </c>
@@ -5157,7 +5219,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -5168,19 +5230,19 @@
         <v>432</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>187</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46249.322544444447</v>
+        <v>46253.60505150463</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>443</v>
       </c>
@@ -5191,7 +5253,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43" t="s">
         <v>436</v>
       </c>
@@ -5203,7 +5265,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="43" t="s">
         <v>444</v>
       </c>
@@ -5215,7 +5277,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>176</v>
       </c>
@@ -5226,7 +5288,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>188</v>
       </c>
@@ -5237,7 +5299,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>195</v>
       </c>
@@ -5248,7 +5310,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>197</v>
       </c>
@@ -5259,7 +5321,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="43" t="s">
         <v>428</v>
       </c>
@@ -5270,7 +5332,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="43" t="s">
         <v>548</v>
       </c>
@@ -5281,7 +5343,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="43" t="s">
         <v>550</v>
       </c>
@@ -5292,7 +5354,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="43" t="s">
         <v>552</v>
       </c>
@@ -5303,7 +5365,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="43" t="s">
         <v>554</v>
       </c>
@@ -5314,7 +5376,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="43" t="s">
         <v>556</v>
       </c>
@@ -5325,7 +5387,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="43" t="s">
         <v>558</v>
       </c>
@@ -5336,7 +5398,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="43" t="s">
         <v>560</v>
       </c>
@@ -5347,7 +5409,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="43" t="s">
         <v>562</v>
       </c>
@@ -5358,7 +5420,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="43" t="s">
         <v>564</v>
       </c>
@@ -5369,7 +5431,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="43" t="s">
         <v>566</v>
       </c>
@@ -5380,7 +5442,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="43" t="s">
         <v>568</v>
       </c>
@@ -5391,7 +5453,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>570</v>
       </c>
@@ -5402,7 +5464,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="74" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="74" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="43" t="s">
         <v>572</v>
       </c>
@@ -5428,35 +5490,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75533AB-3BC5-4EED-85BC-780B8F4A6EA8}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA22"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC22"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.09765625" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.8984375" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.3984375" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62.296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.796875" style="33" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="45.69921875" customWidth="1"/>
-    <col min="25" max="25" width="36.09765625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="57" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="60" customWidth="1"/>
+    <col min="17" max="17" width="63.5" customWidth="1"/>
+    <col min="18" max="18" width="53.5" customWidth="1"/>
+    <col min="19" max="19" width="5" style="33" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="35.33203125" customWidth="1"/>
+    <col min="28" max="29" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="57.75" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>374</v>
       </c>
@@ -5508,38 +5571,44 @@
       <c r="Q1" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="R1" s="23" t="s">
+      <c r="R1" s="41" t="s">
+        <v>427</v>
+      </c>
+      <c r="S1" s="23" t="s">
         <v>418</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="T1" s="23" t="s">
         <v>376</v>
       </c>
-      <c r="T1" s="23" t="s">
+      <c r="U1" s="23" t="s">
         <v>395</v>
       </c>
-      <c r="U1" s="23" t="s">
+      <c r="V1" s="23" t="s">
         <v>378</v>
       </c>
-      <c r="V1" s="23" t="s">
+      <c r="W1" s="23" t="s">
         <v>377</v>
       </c>
-      <c r="W1" s="66" t="s">
+      <c r="X1" s="66" t="s">
         <v>396</v>
       </c>
-      <c r="X1" s="23" t="s">
+      <c r="Y1" s="23" t="s">
         <v>425</v>
       </c>
-      <c r="Y1" s="23" t="s">
+      <c r="Z1" s="23" t="s">
+        <v>605</v>
+      </c>
+      <c r="AA1" s="23" t="s">
         <v>426</v>
       </c>
-      <c r="Z1" s="23" t="s">
+      <c r="AB1" s="23" t="s">
+        <v>606</v>
+      </c>
+      <c r="AC1" s="23" t="s">
         <v>397</v>
       </c>
-      <c r="AA1" s="41" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -5595,42 +5664,48 @@
       <c r="Q2" s="60" t="s">
         <v>510</v>
       </c>
-      <c r="R2" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S2" s="61" t="str">
-        <f t="shared" ref="S2:U14" si="2">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="R2" s="62" t="s">
+        <v>511</v>
+      </c>
+      <c r="S2" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T2" s="61" t="str">
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T2" s="61" t="str">
+      <c r="U2" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U2" s="60" t="str">
+      <c r="V2" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V2" s="42" t="s">
+      <c r="W2" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W2" s="65" t="str">
-        <f t="shared" ref="W2:W14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
+      <c r="X2" s="65" t="str">
+        <f t="shared" ref="X2:X14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
-      <c r="X2" s="42" t="s">
+      <c r="Y2" s="42" t="s">
         <v>584</v>
       </c>
-      <c r="Y2" s="42" t="s">
+      <c r="Z2" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA2" s="42" t="s">
         <v>585</v>
       </c>
-      <c r="Z2" s="42" t="s">
+      <c r="AB2" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC2" s="42" t="s">
         <v>446</v>
       </c>
-      <c r="AA2" s="62" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -5686,42 +5761,48 @@
       <c r="Q3" s="60" t="s">
         <v>513</v>
       </c>
-      <c r="R3" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S3" s="61" t="str">
+      <c r="R3" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="S3" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T3" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T3" s="61" t="str">
+      <c r="U3" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U3" s="60" t="str">
+      <c r="V3" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V3" s="42" t="s">
+      <c r="W3" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W3" s="65" t="str">
+      <c r="X3" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-3</v>
       </c>
-      <c r="X3" s="42" t="s">
+      <c r="Y3" s="42" t="s">
         <v>586</v>
       </c>
-      <c r="Y3" s="42" t="s">
+      <c r="Z3" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA3" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="Z3" s="42" t="s">
+      <c r="AB3" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC3" s="42" t="s">
         <v>447</v>
       </c>
-      <c r="AA3" s="62" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -5777,42 +5858,48 @@
       <c r="Q4" s="60" t="s">
         <v>516</v>
       </c>
-      <c r="R4" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S4" s="61" t="str">
+      <c r="R4" s="62" t="s">
+        <v>517</v>
+      </c>
+      <c r="S4" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T4" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T4" s="61" t="str">
+      <c r="U4" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U4" s="60" t="str">
+      <c r="V4" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V4" s="42" t="s">
+      <c r="W4" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W4" s="65" t="str">
+      <c r="X4" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="X4" s="42" t="s">
+      <c r="Y4" s="42" t="s">
         <v>577</v>
       </c>
-      <c r="Y4" s="42" t="s">
+      <c r="Z4" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA4" s="42" t="s">
         <v>578</v>
       </c>
-      <c r="Z4" s="42" t="s">
+      <c r="AB4" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC4" s="42" t="s">
         <v>448</v>
       </c>
-      <c r="AA4" s="62" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -5868,42 +5955,48 @@
       <c r="Q5" s="60" t="s">
         <v>519</v>
       </c>
-      <c r="R5" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S5" s="61" t="str">
+      <c r="R5" s="62" t="s">
+        <v>520</v>
+      </c>
+      <c r="S5" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T5" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T5" s="61" t="str">
+      <c r="U5" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U5" s="60" t="str">
+      <c r="V5" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V5" s="42" t="s">
+      <c r="W5" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W5" s="65" t="str">
+      <c r="X5" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-5</v>
       </c>
-      <c r="X5" s="42" t="s">
+      <c r="Y5" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="Y5" s="42" t="s">
+      <c r="Z5" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA5" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="Z5" s="42" t="s">
+      <c r="AB5" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC5" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="AA5" s="62" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -5959,42 +6052,48 @@
       <c r="Q6" s="60" t="s">
         <v>522</v>
       </c>
-      <c r="R6" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S6" s="61" t="str">
+      <c r="R6" s="62" t="s">
+        <v>523</v>
+      </c>
+      <c r="S6" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T6" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T6" s="61" t="str">
+      <c r="U6" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U6" s="60" t="str">
+      <c r="V6" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V6" s="42" t="s">
+      <c r="W6" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W6" s="65" t="str">
+      <c r="X6" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="X6" s="42" t="s">
+      <c r="Y6" s="42" t="s">
         <v>577</v>
       </c>
-      <c r="Y6" s="42" t="s">
+      <c r="Z6" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA6" s="42" t="s">
         <v>578</v>
       </c>
-      <c r="Z6" s="42" t="s">
+      <c r="AB6" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC6" s="42" t="s">
         <v>449</v>
       </c>
-      <c r="AA6" s="62" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -6050,42 +6149,48 @@
       <c r="Q7" s="60" t="s">
         <v>525</v>
       </c>
-      <c r="R7" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S7" s="61" t="str">
+      <c r="R7" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="S7" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T7" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T7" s="61" t="str">
+      <c r="U7" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U7" s="60" t="str">
+      <c r="V7" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V7" s="42" t="s">
+      <c r="W7" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W7" s="65" t="str">
+      <c r="X7" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="X7" s="42" t="s">
-        <v>577</v>
-      </c>
       <c r="Y7" s="42" t="s">
         <v>577</v>
       </c>
       <c r="Z7" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA7" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB7" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC7" s="42" t="s">
         <v>450</v>
       </c>
-      <c r="AA7" s="62" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -6141,42 +6246,48 @@
       <c r="Q8" s="60" t="s">
         <v>528</v>
       </c>
-      <c r="R8" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S8" s="61" t="str">
+      <c r="R8" s="62" t="s">
+        <v>529</v>
+      </c>
+      <c r="S8" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T8" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T8" s="61" t="str">
+      <c r="U8" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U8" s="60" t="str">
+      <c r="V8" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V8" s="42" t="s">
+      <c r="W8" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W8" s="65" t="str">
+      <c r="X8" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="X8" s="42" t="s">
-        <v>577</v>
-      </c>
       <c r="Y8" s="42" t="s">
         <v>577</v>
       </c>
       <c r="Z8" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA8" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB8" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC8" s="42" t="s">
         <v>451</v>
       </c>
-      <c r="AA8" s="62" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -6232,42 +6343,48 @@
       <c r="Q9" s="60" t="s">
         <v>531</v>
       </c>
-      <c r="R9" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S9" s="61" t="str">
+      <c r="R9" s="62" t="s">
+        <v>532</v>
+      </c>
+      <c r="S9" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T9" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T9" s="61" t="str">
+      <c r="U9" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U9" s="60" t="str">
+      <c r="V9" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V9" s="42" t="s">
+      <c r="W9" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W9" s="65" t="str">
+      <c r="X9" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="X9" s="42" t="s">
-        <v>577</v>
-      </c>
       <c r="Y9" s="42" t="s">
         <v>577</v>
       </c>
       <c r="Z9" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA9" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB9" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC9" s="42" t="s">
         <v>452</v>
       </c>
-      <c r="AA9" s="62" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -6323,42 +6440,48 @@
       <c r="Q10" s="60" t="s">
         <v>534</v>
       </c>
-      <c r="R10" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S10" s="61" t="str">
+      <c r="R10" s="62" t="s">
+        <v>535</v>
+      </c>
+      <c r="S10" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T10" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T10" s="61" t="str">
+      <c r="U10" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U10" s="60" t="str">
+      <c r="V10" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V10" s="42" t="s">
+      <c r="W10" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W10" s="65" t="str">
+      <c r="X10" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="X10" s="42" t="s">
-        <v>577</v>
-      </c>
       <c r="Y10" s="42" t="s">
         <v>577</v>
       </c>
       <c r="Z10" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA10" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB10" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC10" s="42" t="s">
         <v>453</v>
       </c>
-      <c r="AA10" s="62" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -6414,42 +6537,48 @@
       <c r="Q11" s="60" t="s">
         <v>537</v>
       </c>
-      <c r="R11" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S11" s="61" t="str">
+      <c r="R11" s="62" t="s">
+        <v>538</v>
+      </c>
+      <c r="S11" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T11" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T11" s="61" t="str">
+      <c r="U11" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U11" s="60" t="str">
+      <c r="V11" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V11" s="42" t="s">
+      <c r="W11" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W11" s="65" t="str">
+      <c r="X11" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="X11" s="42" t="s">
-        <v>577</v>
-      </c>
       <c r="Y11" s="42" t="s">
         <v>577</v>
       </c>
       <c r="Z11" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA11" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB11" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC11" s="42" t="s">
         <v>454</v>
       </c>
-      <c r="AA11" s="62" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -6505,42 +6634,48 @@
       <c r="Q12" s="60" t="s">
         <v>540</v>
       </c>
-      <c r="R12" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S12" s="61" t="str">
+      <c r="R12" s="62" t="s">
+        <v>541</v>
+      </c>
+      <c r="S12" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T12" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T12" s="61" t="str">
+      <c r="U12" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U12" s="60" t="str">
+      <c r="V12" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V12" s="42" t="s">
+      <c r="W12" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W12" s="65" t="str">
+      <c r="X12" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-12</v>
       </c>
-      <c r="X12" s="42" t="s">
+      <c r="Y12" s="42" t="s">
         <v>581</v>
       </c>
-      <c r="Y12" s="42" t="s">
+      <c r="Z12" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA12" s="42" t="s">
         <v>588</v>
       </c>
-      <c r="Z12" s="42" t="s">
+      <c r="AB12" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC12" s="42" t="s">
         <v>455</v>
       </c>
-      <c r="AA12" s="62" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -6596,42 +6731,48 @@
       <c r="Q13" s="60" t="s">
         <v>543</v>
       </c>
-      <c r="R13" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S13" s="61" t="str">
+      <c r="R13" s="62" t="s">
+        <v>544</v>
+      </c>
+      <c r="S13" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T13" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T13" s="61" t="str">
+      <c r="U13" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U13" s="60" t="str">
+      <c r="V13" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V13" s="42" t="s">
+      <c r="W13" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W13" s="65" t="str">
+      <c r="X13" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-13</v>
       </c>
-      <c r="X13" s="42" t="s">
+      <c r="Y13" s="42" t="s">
         <v>581</v>
       </c>
-      <c r="Y13" s="42" t="s">
+      <c r="Z13" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA13" s="42" t="s">
         <v>588</v>
       </c>
-      <c r="Z13" s="42" t="s">
+      <c r="AB13" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC13" s="42" t="s">
         <v>456</v>
       </c>
-      <c r="AA13" s="62" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -6687,42 +6828,48 @@
       <c r="Q14" s="60" t="s">
         <v>546</v>
       </c>
-      <c r="R14" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S14" s="61" t="str">
+      <c r="R14" s="62" t="s">
+        <v>547</v>
+      </c>
+      <c r="S14" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T14" s="61" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T14" s="61" t="str">
+      <c r="U14" s="61" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U14" s="60" t="str">
+      <c r="V14" s="60" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V14" s="42" t="s">
+      <c r="W14" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W14" s="65" t="str">
+      <c r="X14" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-14</v>
       </c>
-      <c r="X14" s="75" t="s">
+      <c r="Y14" s="75" t="s">
         <v>582</v>
       </c>
-      <c r="Y14" s="76" t="s">
+      <c r="Z14" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA14" s="76" t="s">
         <v>583</v>
       </c>
-      <c r="Z14" s="42" t="s">
+      <c r="AB14" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC14" s="42" t="s">
         <v>457</v>
       </c>
-      <c r="AA14" s="62" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -6775,47 +6922,51 @@
       <c r="P15" s="42" t="s">
         <v>488</v>
       </c>
-      <c r="Q15" s="42" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","es")</f>
-        <v>Fase de programación</v>
+      <c r="Q15" s="42" t="s">
+        <v>597</v>
       </c>
       <c r="R15" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S15" s="61" t="str">
-        <f t="shared" ref="S15:U17" si="6">SUBSTITUTE(C15, "_", " ")</f>
+        <v>589</v>
+      </c>
+      <c r="S15" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T15" s="61" t="str">
+        <f t="shared" ref="T15:V17" si="6">SUBSTITUTE(C15, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T15" s="61" t="str">
+      <c r="U15" s="61" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U15" s="60" t="str">
+      <c r="V15" s="60" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="V15" s="42" t="s">
+      <c r="W15" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W15" s="65" t="str">
-        <f t="shared" ref="W15:W22" si="7">CONCATENATE("Key-ABNT-",A15)</f>
+      <c r="X15" s="65" t="str">
+        <f t="shared" ref="X15:X22" si="7">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
       </c>
-      <c r="X15" s="42" t="s">
+      <c r="Y15" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="Y15" s="42" t="s">
+      <c r="Z15" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA15" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="Z15" s="61" t="s">
+      <c r="AB15" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC15" s="61" t="s">
         <v>496</v>
       </c>
-      <c r="AA15" s="42" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Programming Phase</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -6868,47 +7019,51 @@
       <c r="P16" s="60" t="s">
         <v>495</v>
       </c>
-      <c r="Q16" s="42" t="str">
-        <f t="shared" ref="Q16:Q22" si="8">_xlfn.TRANSLATE(P16,"pt","es")</f>
-        <v>Fase de Estudios Preliminares</v>
+      <c r="Q16" s="42" t="s">
+        <v>598</v>
       </c>
       <c r="R16" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S16" s="61" t="str">
+        <v>590</v>
+      </c>
+      <c r="S16" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T16" s="61" t="str">
         <f t="shared" si="6"/>
         <v>Normativos</v>
       </c>
-      <c r="T16" s="61" t="str">
+      <c r="U16" s="61" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U16" s="60" t="str">
+      <c r="V16" s="60" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="V16" s="42" t="s">
+      <c r="W16" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W16" s="65" t="str">
+      <c r="X16" s="65" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-16</v>
       </c>
-      <c r="X16" s="42" t="s">
+      <c r="Y16" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="Y16" s="42" t="s">
+      <c r="Z16" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA16" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="Z16" s="61" t="s">
+      <c r="AB16" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC16" s="61" t="s">
         <v>497</v>
       </c>
-      <c r="AA16" s="42" t="str">
-        <f t="shared" ref="AA16:AA22" si="9">_xlfn.TRANSLATE(P16,"pt","en")</f>
-        <v>Preliminary Studies Phase</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -6961,47 +7116,51 @@
       <c r="P17" s="60" t="s">
         <v>489</v>
       </c>
-      <c r="Q17" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Fase del proyecto</v>
+      <c r="Q17" s="42" t="s">
+        <v>599</v>
       </c>
       <c r="R17" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S17" s="61" t="str">
+        <v>591</v>
+      </c>
+      <c r="S17" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T17" s="61" t="str">
         <f t="shared" si="6"/>
         <v>Normativos</v>
       </c>
-      <c r="T17" s="61" t="str">
+      <c r="U17" s="61" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U17" s="60" t="str">
+      <c r="V17" s="60" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="V17" s="42" t="s">
+      <c r="W17" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W17" s="65" t="str">
+      <c r="X17" s="65" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-17</v>
       </c>
-      <c r="X17" s="42" t="s">
+      <c r="Y17" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="Y17" s="42" t="s">
+      <c r="Z17" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA17" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="Z17" s="61" t="s">
+      <c r="AB17" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC17" s="61" t="s">
         <v>498</v>
       </c>
-      <c r="AA17" s="42" t="str">
-        <f t="shared" si="9"/>
-        <v>Project Phase</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -7054,47 +7213,51 @@
       <c r="P18" s="60" t="s">
         <v>494</v>
       </c>
-      <c r="Q18" s="42" t="str">
+      <c r="Q18" s="42" t="s">
+        <v>600</v>
+      </c>
+      <c r="R18" s="42" t="s">
+        <v>592</v>
+      </c>
+      <c r="S18" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T18" s="61" t="str">
+        <f t="shared" ref="T18:V22" si="8">SUBSTITUTE(C18, "_", " ")</f>
+        <v>Normativos</v>
+      </c>
+      <c r="U18" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Fase de subasta</v>
-      </c>
-      <c r="R18" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S18" s="61" t="str">
-        <f t="shared" ref="S18:U22" si="10">SUBSTITUTE(C18, "_", " ")</f>
-        <v>Normativos</v>
-      </c>
-      <c r="T18" s="61" t="str">
-        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U18" s="60" t="str">
-        <f t="shared" si="10"/>
+      <c r="V18" s="60" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="V18" s="42" t="s">
+      <c r="W18" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W18" s="65" t="str">
+      <c r="X18" s="65" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-18</v>
       </c>
-      <c r="X18" s="42" t="s">
+      <c r="Y18" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="Y18" s="42" t="s">
+      <c r="Z18" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA18" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="Z18" s="61" t="s">
+      <c r="AB18" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC18" s="61" t="s">
         <v>499</v>
       </c>
-      <c r="AA18" s="42" t="str">
-        <f t="shared" si="9"/>
-        <v>Bidding Phase</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -7147,47 +7310,51 @@
       <c r="P19" s="60" t="s">
         <v>493</v>
       </c>
-      <c r="Q19" s="42" t="str">
+      <c r="Q19" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="R19" s="42" t="s">
+        <v>593</v>
+      </c>
+      <c r="S19" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T19" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Fase de construcción</v>
-      </c>
-      <c r="R19" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S19" s="61" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T19" s="61" t="str">
-        <f t="shared" si="10"/>
+      <c r="U19" s="61" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U19" s="60" t="str">
-        <f t="shared" si="10"/>
+      <c r="V19" s="60" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="V19" s="42" t="s">
+      <c r="W19" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W19" s="65" t="str">
+      <c r="X19" s="65" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-19</v>
       </c>
-      <c r="X19" s="42" t="s">
+      <c r="Y19" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="Y19" s="42" t="s">
+      <c r="Z19" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA19" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="Z19" s="61" t="s">
+      <c r="AB19" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC19" s="61" t="s">
         <v>503</v>
       </c>
-      <c r="AA19" s="42" t="str">
-        <f t="shared" si="9"/>
-        <v>Construction Phase</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="57">
         <v>20</v>
       </c>
@@ -7240,47 +7407,51 @@
       <c r="P20" s="60" t="s">
         <v>490</v>
       </c>
-      <c r="Q20" s="42" t="str">
+      <c r="Q20" s="42" t="s">
+        <v>602</v>
+      </c>
+      <c r="R20" s="42" t="s">
+        <v>594</v>
+      </c>
+      <c r="S20" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T20" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Fase de puesta en servicio</v>
-      </c>
-      <c r="R20" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S20" s="61" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T20" s="61" t="str">
-        <f t="shared" si="10"/>
+      <c r="U20" s="61" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U20" s="60" t="str">
-        <f t="shared" si="10"/>
+      <c r="V20" s="60" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="V20" s="42" t="s">
+      <c r="W20" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W20" s="65" t="str">
+      <c r="X20" s="65" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-20</v>
       </c>
-      <c r="X20" s="42" t="s">
+      <c r="Y20" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="Y20" s="42" t="s">
+      <c r="Z20" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA20" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="Z20" s="61" t="s">
+      <c r="AB20" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC20" s="61" t="s">
         <v>500</v>
       </c>
-      <c r="AA20" s="42" t="str">
-        <f t="shared" si="9"/>
-        <v>Commissioning Phase</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="57">
         <v>21</v>
       </c>
@@ -7333,47 +7504,51 @@
       <c r="P21" s="60" t="s">
         <v>491</v>
       </c>
-      <c r="Q21" s="42" t="str">
+      <c r="Q21" s="42" t="s">
+        <v>603</v>
+      </c>
+      <c r="R21" s="42" t="s">
+        <v>595</v>
+      </c>
+      <c r="S21" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T21" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Fase de Operación</v>
-      </c>
-      <c r="R21" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S21" s="61" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T21" s="61" t="str">
-        <f t="shared" si="10"/>
+      <c r="U21" s="61" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U21" s="60" t="str">
-        <f t="shared" si="10"/>
+      <c r="V21" s="60" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="V21" s="42" t="s">
+      <c r="W21" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W21" s="65" t="str">
+      <c r="X21" s="65" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-21</v>
       </c>
-      <c r="X21" s="42" t="s">
+      <c r="Y21" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="Y21" s="42" t="s">
+      <c r="Z21" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA21" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="Z21" s="61" t="s">
+      <c r="AB21" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC21" s="61" t="s">
         <v>501</v>
       </c>
-      <c r="AA21" s="42" t="str">
-        <f t="shared" si="9"/>
-        <v>Operation Phase</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="57">
         <v>22</v>
       </c>
@@ -7426,63 +7601,72 @@
       <c r="P22" s="60" t="s">
         <v>492</v>
       </c>
-      <c r="Q22" s="42" t="str">
+      <c r="Q22" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="R22" s="42" t="s">
+        <v>596</v>
+      </c>
+      <c r="S22" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="T22" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Fase de cierre y demolición</v>
-      </c>
-      <c r="R22" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S22" s="61" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T22" s="61" t="str">
-        <f t="shared" si="10"/>
+      <c r="U22" s="61" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U22" s="60" t="str">
-        <f t="shared" si="10"/>
+      <c r="V22" s="60" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="V22" s="42" t="s">
+      <c r="W22" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="W22" s="65" t="str">
+      <c r="X22" s="65" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-22</v>
       </c>
-      <c r="X22" s="42" t="s">
+      <c r="Y22" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="Y22" s="42" t="s">
+      <c r="Z22" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AA22" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="Z22" s="61" t="s">
+      <c r="AB22" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC22" s="61" t="s">
         <v>502</v>
-      </c>
-      <c r="AA22" s="42" t="str">
-        <f t="shared" si="9"/>
-        <v>Closure and Demolition Phase</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="20" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y2">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+  <conditionalFormatting sqref="Y2 AA2">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA22 A2:B22">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B22">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R22">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7497,13 +7681,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A4D5B2-E607-43E1-969D-E9BC12588F0D}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
         <v>375</v>
       </c>
@@ -7568,7 +7752,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -7650,13 +7834,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50BE4DF8-DB25-47BD-BFAE-132A16409236}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.796875" customWidth="1"/>
+    <col min="2" max="3" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -7667,7 +7851,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -7692,34 +7876,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y169"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.69921875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.5" style="38" customWidth="1"/>
     <col min="7" max="7" width="9" style="38" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4" style="38" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" style="38" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.5" style="38" customWidth="1"/>
-    <col min="11" max="11" width="7.19921875" style="38" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.1640625" style="38" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.19921875" style="38" customWidth="1"/>
-    <col min="14" max="14" width="5.69921875" style="38" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" style="38" customWidth="1"/>
+    <col min="14" max="14" width="5.6640625" style="38" customWidth="1"/>
     <col min="15" max="15" width="36" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="8.796875" style="38" customWidth="1"/>
+    <col min="16" max="19" width="8.83203125" style="38" customWidth="1"/>
     <col min="20" max="20" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>189</v>
       </c>
@@ -7796,7 +7980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -7873,7 +8057,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -7950,7 +8134,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -8027,7 +8211,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -8104,7 +8288,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -8181,7 +8365,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -8258,7 +8442,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -8335,7 +8519,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -8412,7 +8596,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -8489,7 +8673,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -8566,7 +8750,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -8643,7 +8827,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -8720,7 +8904,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -8797,7 +8981,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -8874,7 +9058,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>16</v>
       </c>
@@ -8951,7 +9135,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>17</v>
       </c>
@@ -9028,7 +9212,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>18</v>
       </c>
@@ -9105,7 +9289,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>19</v>
       </c>
@@ -9182,7 +9366,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>20</v>
       </c>
@@ -9259,7 +9443,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>21</v>
       </c>
@@ -9336,7 +9520,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>22</v>
       </c>
@@ -9413,7 +9597,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>23</v>
       </c>
@@ -9490,7 +9674,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>24</v>
       </c>
@@ -9567,7 +9751,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>25</v>
       </c>
@@ -9644,7 +9828,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>26</v>
       </c>
@@ -9721,7 +9905,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>27</v>
       </c>
@@ -9798,7 +9982,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>28</v>
       </c>
@@ -9875,7 +10059,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>29</v>
       </c>
@@ -9952,7 +10136,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>30</v>
       </c>
@@ -10029,7 +10213,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>31</v>
       </c>
@@ -10106,7 +10290,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>32</v>
       </c>
@@ -10183,7 +10367,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>33</v>
       </c>
@@ -10260,7 +10444,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>34</v>
       </c>
@@ -10337,7 +10521,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>35</v>
       </c>
@@ -10414,7 +10598,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>36</v>
       </c>
@@ -10491,7 +10675,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>37</v>
       </c>
@@ -10568,7 +10752,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>38</v>
       </c>
@@ -10645,7 +10829,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>39</v>
       </c>
@@ -10722,7 +10906,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>40</v>
       </c>
@@ -10799,7 +10983,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>41</v>
       </c>
@@ -10876,7 +11060,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>42</v>
       </c>
@@ -10953,7 +11137,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>43</v>
       </c>
@@ -11030,7 +11214,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>44</v>
       </c>
@@ -11107,7 +11291,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>45</v>
       </c>
@@ -11184,7 +11368,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>46</v>
       </c>
@@ -11261,7 +11445,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>47</v>
       </c>
@@ -11338,7 +11522,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>48</v>
       </c>
@@ -11415,7 +11599,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>49</v>
       </c>
@@ -11492,7 +11676,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>50</v>
       </c>
@@ -11569,7 +11753,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>51</v>
       </c>
@@ -11646,7 +11830,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>52</v>
       </c>
@@ -11723,7 +11907,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>53</v>
       </c>
@@ -11800,7 +11984,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>54</v>
       </c>
@@ -11877,7 +12061,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>55</v>
       </c>
@@ -11954,7 +12138,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>56</v>
       </c>
@@ -12031,7 +12215,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>57</v>
       </c>
@@ -12108,7 +12292,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>58</v>
       </c>
@@ -12185,7 +12369,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>59</v>
       </c>
@@ -12262,7 +12446,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>60</v>
       </c>
@@ -12339,7 +12523,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>61</v>
       </c>
@@ -12416,7 +12600,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>62</v>
       </c>
@@ -12493,7 +12677,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>63</v>
       </c>
@@ -12570,7 +12754,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>64</v>
       </c>
@@ -12647,7 +12831,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>65</v>
       </c>
@@ -12724,7 +12908,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>66</v>
       </c>
@@ -12801,7 +12985,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>67</v>
       </c>
@@ -12878,7 +13062,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>68</v>
       </c>
@@ -12955,7 +13139,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>69</v>
       </c>
@@ -13032,7 +13216,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>70</v>
       </c>
@@ -13109,7 +13293,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="8">
         <v>71</v>
       </c>
@@ -13186,7 +13370,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>72</v>
       </c>
@@ -13263,7 +13447,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="8">
         <v>73</v>
       </c>
@@ -13340,7 +13524,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="8">
         <v>74</v>
       </c>
@@ -13417,7 +13601,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>75</v>
       </c>
@@ -13494,7 +13678,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="8">
         <v>76</v>
       </c>
@@ -13571,7 +13755,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="8">
         <v>77</v>
       </c>
@@ -13648,7 +13832,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="8">
         <v>78</v>
       </c>
@@ -13725,7 +13909,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="8">
         <v>79</v>
       </c>
@@ -13802,7 +13986,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="8">
         <v>80</v>
       </c>
@@ -13879,7 +14063,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="8">
         <v>81</v>
       </c>
@@ -13956,7 +14140,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="8">
         <v>82</v>
       </c>
@@ -14033,7 +14217,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="8">
         <v>83</v>
       </c>
@@ -14110,7 +14294,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="8">
         <v>84</v>
       </c>
@@ -14187,7 +14371,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="8">
         <v>85</v>
       </c>
@@ -14264,7 +14448,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="8">
         <v>86</v>
       </c>
@@ -14341,7 +14525,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="8">
         <v>87</v>
       </c>
@@ -14418,7 +14602,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="8">
         <v>88</v>
       </c>
@@ -14495,7 +14679,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
         <v>89</v>
       </c>
@@ -14572,7 +14756,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
         <v>90</v>
       </c>
@@ -14649,7 +14833,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
         <v>91</v>
       </c>
@@ -14726,7 +14910,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="8">
         <v>92</v>
       </c>
@@ -14803,7 +14987,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="8">
         <v>93</v>
       </c>
@@ -14880,7 +15064,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="8">
         <v>94</v>
       </c>
@@ -14957,7 +15141,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="8">
         <v>95</v>
       </c>
@@ -15034,7 +15218,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="8">
         <v>96</v>
       </c>
@@ -15111,7 +15295,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="8">
         <v>97</v>
       </c>
@@ -15188,7 +15372,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="8">
         <v>98</v>
       </c>
@@ -15265,7 +15449,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="8">
         <v>99</v>
       </c>
@@ -15342,7 +15526,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="8">
         <v>100</v>
       </c>
@@ -15419,7 +15603,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="8">
         <v>101</v>
       </c>
@@ -15496,7 +15680,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="8">
         <v>102</v>
       </c>
@@ -15573,7 +15757,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="8">
         <v>103</v>
       </c>
@@ -15650,7 +15834,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="8">
         <v>104</v>
       </c>
@@ -15727,7 +15911,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="8">
         <v>105</v>
       </c>
@@ -15804,7 +15988,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="8">
         <v>106</v>
       </c>
@@ -15881,7 +16065,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="8">
         <v>107</v>
       </c>
@@ -15958,7 +16142,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="8">
         <v>108</v>
       </c>
@@ -16035,7 +16219,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="8">
         <v>109</v>
       </c>
@@ -16112,7 +16296,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="8">
         <v>110</v>
       </c>
@@ -16189,7 +16373,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="8">
         <v>111</v>
       </c>
@@ -16266,7 +16450,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="8">
         <v>112</v>
       </c>
@@ -16343,7 +16527,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="8">
         <v>113</v>
       </c>
@@ -16420,7 +16604,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="8">
         <v>114</v>
       </c>
@@ -16497,7 +16681,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="8">
         <v>115</v>
       </c>
@@ -16574,7 +16758,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="8">
         <v>116</v>
       </c>
@@ -16651,7 +16835,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="8">
         <v>117</v>
       </c>
@@ -16728,7 +16912,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="8">
         <v>118</v>
       </c>
@@ -16805,7 +16989,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="8">
         <v>119</v>
       </c>
@@ -16882,7 +17066,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="8">
         <v>120</v>
       </c>
@@ -16959,7 +17143,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="8">
         <v>121</v>
       </c>
@@ -17036,7 +17220,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="8">
         <v>122</v>
       </c>
@@ -17113,7 +17297,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="8">
         <v>123</v>
       </c>
@@ -17190,7 +17374,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="8">
         <v>124</v>
       </c>
@@ -17267,7 +17451,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="8">
         <v>125</v>
       </c>
@@ -17344,7 +17528,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="8">
         <v>126</v>
       </c>
@@ -17421,7 +17605,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="8">
         <v>127</v>
       </c>
@@ -17498,7 +17682,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="8">
         <v>128</v>
       </c>
@@ -17575,7 +17759,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="8">
         <v>129</v>
       </c>
@@ -17652,7 +17836,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="8">
         <v>130</v>
       </c>
@@ -17729,7 +17913,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="8">
         <v>131</v>
       </c>
@@ -17806,7 +17990,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
         <v>132</v>
       </c>
@@ -17883,7 +18067,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <v>133</v>
       </c>
@@ -17960,7 +18144,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <v>134</v>
       </c>
@@ -18037,7 +18221,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <v>135</v>
       </c>
@@ -18114,7 +18298,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <v>136</v>
       </c>
@@ -18191,7 +18375,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <v>137</v>
       </c>
@@ -18268,7 +18452,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <v>138</v>
       </c>
@@ -18345,7 +18529,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="8">
         <v>139</v>
       </c>
@@ -18422,7 +18606,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="8">
         <v>140</v>
       </c>
@@ -18499,7 +18683,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="8">
         <v>141</v>
       </c>
@@ -18576,7 +18760,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="8">
         <v>142</v>
       </c>
@@ -18653,7 +18837,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="8">
         <v>143</v>
       </c>
@@ -18730,7 +18914,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="8">
         <v>144</v>
       </c>
@@ -18807,7 +18991,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="8">
         <v>145</v>
       </c>
@@ -18884,7 +19068,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
         <v>146</v>
       </c>
@@ -18961,7 +19145,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <v>147</v>
       </c>
@@ -19038,7 +19222,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <v>148</v>
       </c>
@@ -19115,7 +19299,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <v>149</v>
       </c>
@@ -19192,7 +19376,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <v>150</v>
       </c>
@@ -19269,7 +19453,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <v>151</v>
       </c>
@@ -19346,7 +19530,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <v>152</v>
       </c>
@@ -19423,7 +19607,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <v>153</v>
       </c>
@@ -19500,7 +19684,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <v>154</v>
       </c>
@@ -19577,7 +19761,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <v>155</v>
       </c>
@@ -19654,7 +19838,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <v>156</v>
       </c>
@@ -19731,7 +19915,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <v>157</v>
       </c>
@@ -19808,7 +19992,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <v>158</v>
       </c>
@@ -19885,7 +20069,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <v>159</v>
       </c>
@@ -19962,7 +20146,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <v>160</v>
       </c>
@@ -20039,7 +20223,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <v>161</v>
       </c>
@@ -20116,7 +20300,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <v>162</v>
       </c>
@@ -20193,7 +20377,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <v>163</v>
       </c>
@@ -20270,7 +20454,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <v>164</v>
       </c>
@@ -20347,7 +20531,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="8">
         <v>165</v>
       </c>
@@ -20424,7 +20608,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="8">
         <v>166</v>
       </c>
@@ -20501,7 +20685,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
         <v>167</v>
       </c>
@@ -20578,7 +20762,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
         <v>168</v>
       </c>
@@ -20655,7 +20839,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
         <v>169</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6956DE4B-ED34-41A7-B933-C75D5FC821F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34E0B03-B7FA-487E-9A82-0A0D093A3477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5847" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5842" uniqueCount="637">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1986,19 +1986,22 @@
     <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
   </si>
   <si>
-    <t>é.rvt.ambiente</t>
-  </si>
-  <si>
-    <t>é.rvt.andar</t>
-  </si>
-  <si>
-    <t>é.rvt.elemento</t>
-  </si>
-  <si>
-    <t>é.rvt.tipo</t>
-  </si>
-  <si>
-    <t>é.rvt.material</t>
+    <t>é.selecionado.por</t>
+  </si>
+  <si>
+    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
+  </si>
+  <si>
+    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
+  </si>
+  <si>
+    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
+  </si>
+  <si>
+    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
+  </si>
+  <si>
+    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
   </si>
 </sst>
 </file>
@@ -2120,7 +2123,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2295,6 +2298,18 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -2388,7 +2403,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2628,13 +2643,27 @@
     <xf numFmtId="0" fontId="5" fillId="29" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="109">
+  <dxfs count="112">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2664,7 +2693,23 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -3079,12 +3124,12 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor theme="9" tint="0.59999389629810485"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -3097,6 +3142,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3225,12 +3272,12 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor theme="9" tint="0.59999389629810485"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -3243,6 +3290,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3371,12 +3420,12 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor theme="9" tint="0.59999389629810485"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -3389,6 +3438,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3517,12 +3568,12 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor theme="9" tint="0.59999389629810485"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -3535,6 +3586,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -5390,39 +5443,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AE174" headerRowCount="0" totalsRowShown="0" headerRowDxfId="108" dataDxfId="106" headerRowBorderDxfId="107" tableBorderDxfId="105" totalsRowBorderDxfId="104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AE174" headerRowCount="0" totalsRowShown="0" headerRowDxfId="111" dataDxfId="109" headerRowBorderDxfId="110" tableBorderDxfId="108" totalsRowBorderDxfId="107">
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="103" dataDxfId="102"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="101" dataDxfId="100"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="99" dataDxfId="98"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="97" dataDxfId="96"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="95" dataDxfId="94"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="93" dataDxfId="92"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="91" dataDxfId="90"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="89" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="87" dataDxfId="86"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="85" dataDxfId="84"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="83" dataDxfId="82"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="81" dataDxfId="80"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="79" dataDxfId="78"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="77" dataDxfId="76"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="75" dataDxfId="74"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="73" dataDxfId="72"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="71" dataDxfId="70"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{67BF49D0-5BD9-4C65-9F7F-321F877F93D3}" name="Coluna22" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="27" xr3:uid="{7A57466B-85C9-4F19-B457-DD53AF8B8B43}" name="Coluna23" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="28" xr3:uid="{6D0F7AE3-FE22-4AE0-AE3D-EA7C26DBB834}" name="Coluna24" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="29" xr3:uid="{B5303D9A-769C-4D11-ADE2-1AAE03620B1A}" name="Coluna25" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="30" xr3:uid="{4F8D4348-881E-4EAD-A52A-10BC46F48D0D}" name="Coluna26" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="31" xr3:uid="{C0E47BB3-37C7-4FBB-B9CB-C678EBFDA4CA}" name="Coluna27" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="32" xr3:uid="{6015C5FC-5AAA-4A27-A4C7-2E5CBBCB9787}" name="Coluna28" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="33" xr3:uid="{ECDE8196-C351-4A04-9C91-30718C7DA362}" name="Coluna29" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="106" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="104" dataDxfId="103"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="102" dataDxfId="101"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="100" dataDxfId="99"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="98" dataDxfId="97"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="96" dataDxfId="95"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="94" dataDxfId="93"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="92" dataDxfId="91"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="90" dataDxfId="89"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="88" dataDxfId="87"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="86" dataDxfId="85"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="84" dataDxfId="83"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="82" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="80" dataDxfId="79"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="78" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="76" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="74" dataDxfId="73"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="72" dataDxfId="71"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="70" dataDxfId="69"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="68" dataDxfId="67"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="66" dataDxfId="65"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{67BF49D0-5BD9-4C65-9F7F-321F877F93D3}" name="Coluna22" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="27" xr3:uid="{7A57466B-85C9-4F19-B457-DD53AF8B8B43}" name="Coluna23" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="28" xr3:uid="{6D0F7AE3-FE22-4AE0-AE3D-EA7C26DBB834}" name="Coluna24" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="29" xr3:uid="{B5303D9A-769C-4D11-ADE2-1AAE03620B1A}" name="Coluna25" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="30" xr3:uid="{4F8D4348-881E-4EAD-A52A-10BC46F48D0D}" name="Coluna26" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="31" xr3:uid="{C0E47BB3-37C7-4FBB-B9CB-C678EBFDA4CA}" name="Coluna27" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="32" xr3:uid="{6015C5FC-5AAA-4A27-A4C7-2E5CBBCB9787}" name="Coluna28" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="33" xr3:uid="{ECDE8196-C351-4A04-9C91-30718C7DA362}" name="Coluna29" headerRowDxfId="46" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5949,7 +6002,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46257.699642824075</v>
+        <v>46257.755699652778</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
@@ -8457,29 +8510,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B23">
-    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="40" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="39" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="33" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8632,7 +8685,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8677,7 +8730,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8707,20 +8760,20 @@
     <col min="14" max="14" width="5.296875" style="38" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="43.09765625" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.3984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.8984375" style="38" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="79.3984375" style="38" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" style="38" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="4.8984375" style="38" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.09765625" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11" style="2" customWidth="1"/>
     <col min="23" max="23" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11" style="2" customWidth="1"/>
     <col min="25" max="25" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11" style="2" customWidth="1"/>
     <col min="27" max="27" width="7.296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11" style="2" customWidth="1"/>
     <col min="29" max="29" width="7.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11" style="2" customWidth="1"/>
     <col min="31" max="31" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="32" max="16384" width="11.5" style="2"/>
   </cols>
@@ -9081,25 +9134,25 @@
         <v>615</v>
       </c>
       <c r="X4" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y4" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z4" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA4" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB4" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC4" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD4" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE4" s="62" t="s">
         <v>628</v>
@@ -9176,25 +9229,25 @@
         <v>615</v>
       </c>
       <c r="X5" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y5" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z5" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA5" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB5" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC5" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD5" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE5" s="62" t="s">
         <v>628</v>
@@ -9271,25 +9324,25 @@
         <v>615</v>
       </c>
       <c r="X6" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y6" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z6" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA6" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB6" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC6" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD6" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE6" s="62" t="s">
         <v>628</v>
@@ -9366,25 +9419,25 @@
         <v>615</v>
       </c>
       <c r="X7" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y7" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z7" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA7" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB7" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC7" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD7" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE7" s="62" t="s">
         <v>628</v>
@@ -9461,25 +9514,25 @@
         <v>615</v>
       </c>
       <c r="X8" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y8" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z8" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA8" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB8" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC8" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD8" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE8" s="62" t="s">
         <v>628</v>
@@ -9556,25 +9609,25 @@
         <v>615</v>
       </c>
       <c r="X9" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y9" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z9" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA9" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB9" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC9" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD9" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE9" s="62" t="s">
         <v>628</v>
@@ -9651,25 +9704,25 @@
         <v>615</v>
       </c>
       <c r="X10" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y10" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z10" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA10" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB10" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC10" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD10" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE10" s="62" t="s">
         <v>628</v>
@@ -9746,25 +9799,25 @@
         <v>615</v>
       </c>
       <c r="X11" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y11" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z11" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA11" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB11" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC11" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD11" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE11" s="62" t="s">
         <v>628</v>
@@ -9841,25 +9894,25 @@
         <v>615</v>
       </c>
       <c r="X12" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y12" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z12" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA12" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB12" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC12" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD12" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE12" s="62" t="s">
         <v>628</v>
@@ -9936,25 +9989,25 @@
         <v>615</v>
       </c>
       <c r="X13" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y13" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z13" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA13" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB13" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC13" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD13" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE13" s="62" t="s">
         <v>628</v>
@@ -10031,25 +10084,25 @@
         <v>615</v>
       </c>
       <c r="X14" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y14" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z14" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA14" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB14" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC14" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD14" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE14" s="62" t="s">
         <v>628</v>
@@ -10126,25 +10179,25 @@
         <v>615</v>
       </c>
       <c r="X15" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y15" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z15" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA15" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB15" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC15" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD15" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE15" s="62" t="s">
         <v>628</v>
@@ -10221,25 +10274,25 @@
         <v>615</v>
       </c>
       <c r="X16" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y16" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z16" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA16" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB16" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC16" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD16" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE16" s="62" t="s">
         <v>628</v>
@@ -10316,25 +10369,25 @@
         <v>615</v>
       </c>
       <c r="X17" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y17" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z17" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA17" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB17" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC17" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD17" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE17" s="62" t="s">
         <v>628</v>
@@ -10411,25 +10464,25 @@
         <v>615</v>
       </c>
       <c r="X18" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y18" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z18" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA18" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB18" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC18" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD18" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE18" s="62" t="s">
         <v>628</v>
@@ -10506,25 +10559,25 @@
         <v>615</v>
       </c>
       <c r="X19" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y19" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z19" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA19" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB19" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC19" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD19" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE19" s="62" t="s">
         <v>628</v>
@@ -10601,25 +10654,25 @@
         <v>615</v>
       </c>
       <c r="X20" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y20" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z20" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA20" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB20" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC20" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD20" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE20" s="62" t="s">
         <v>628</v>
@@ -10696,25 +10749,25 @@
         <v>615</v>
       </c>
       <c r="X21" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y21" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z21" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA21" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB21" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC21" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD21" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE21" s="62" t="s">
         <v>628</v>
@@ -10791,25 +10844,25 @@
         <v>615</v>
       </c>
       <c r="X22" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y22" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z22" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA22" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB22" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC22" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD22" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE22" s="62" t="s">
         <v>628</v>
@@ -10886,25 +10939,25 @@
         <v>615</v>
       </c>
       <c r="X23" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y23" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z23" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA23" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB23" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC23" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD23" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE23" s="62" t="s">
         <v>628</v>
@@ -10981,25 +11034,25 @@
         <v>615</v>
       </c>
       <c r="X24" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y24" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z24" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA24" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB24" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC24" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD24" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE24" s="62" t="s">
         <v>628</v>
@@ -11076,25 +11129,25 @@
         <v>615</v>
       </c>
       <c r="X25" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y25" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z25" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA25" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB25" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC25" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD25" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE25" s="62" t="s">
         <v>628</v>
@@ -11171,25 +11224,25 @@
         <v>615</v>
       </c>
       <c r="X26" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y26" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z26" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA26" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB26" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC26" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD26" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE26" s="62" t="s">
         <v>628</v>
@@ -11266,25 +11319,25 @@
         <v>615</v>
       </c>
       <c r="X27" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y27" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z27" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA27" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB27" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC27" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD27" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE27" s="62" t="s">
         <v>628</v>
@@ -11361,25 +11414,25 @@
         <v>615</v>
       </c>
       <c r="X28" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y28" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z28" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA28" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB28" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC28" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD28" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE28" s="62" t="s">
         <v>628</v>
@@ -11456,25 +11509,25 @@
         <v>615</v>
       </c>
       <c r="X29" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y29" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z29" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA29" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB29" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC29" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD29" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE29" s="62" t="s">
         <v>628</v>
@@ -11551,25 +11604,25 @@
         <v>615</v>
       </c>
       <c r="X30" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y30" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z30" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA30" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB30" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC30" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD30" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE30" s="62" t="s">
         <v>628</v>
@@ -11646,25 +11699,25 @@
         <v>615</v>
       </c>
       <c r="X31" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y31" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z31" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA31" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB31" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC31" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD31" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE31" s="62" t="s">
         <v>628</v>
@@ -11741,25 +11794,25 @@
         <v>615</v>
       </c>
       <c r="X32" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y32" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z32" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA32" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB32" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC32" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD32" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE32" s="62" t="s">
         <v>628</v>
@@ -11836,25 +11889,25 @@
         <v>615</v>
       </c>
       <c r="X33" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y33" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z33" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA33" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB33" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC33" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD33" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE33" s="62" t="s">
         <v>628</v>
@@ -11931,25 +11984,25 @@
         <v>615</v>
       </c>
       <c r="X34" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y34" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z34" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA34" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB34" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC34" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD34" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE34" s="62" t="s">
         <v>628</v>
@@ -12026,25 +12079,25 @@
         <v>615</v>
       </c>
       <c r="X35" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y35" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z35" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA35" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB35" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC35" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD35" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE35" s="62" t="s">
         <v>628</v>
@@ -12121,25 +12174,25 @@
         <v>615</v>
       </c>
       <c r="X36" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y36" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z36" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA36" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB36" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC36" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD36" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE36" s="62" t="s">
         <v>628</v>
@@ -12216,25 +12269,25 @@
         <v>615</v>
       </c>
       <c r="X37" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y37" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z37" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA37" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB37" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC37" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD37" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE37" s="62" t="s">
         <v>628</v>
@@ -12311,25 +12364,25 @@
         <v>615</v>
       </c>
       <c r="X38" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y38" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z38" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA38" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB38" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC38" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD38" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE38" s="62" t="s">
         <v>628</v>
@@ -12406,25 +12459,25 @@
         <v>615</v>
       </c>
       <c r="X39" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y39" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z39" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA39" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB39" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC39" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD39" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE39" s="62" t="s">
         <v>628</v>
@@ -12501,25 +12554,25 @@
         <v>615</v>
       </c>
       <c r="X40" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y40" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z40" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA40" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB40" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC40" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD40" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE40" s="62" t="s">
         <v>628</v>
@@ -12596,25 +12649,25 @@
         <v>615</v>
       </c>
       <c r="X41" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y41" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z41" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA41" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB41" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC41" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD41" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE41" s="62" t="s">
         <v>628</v>
@@ -12691,25 +12744,25 @@
         <v>615</v>
       </c>
       <c r="X42" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y42" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z42" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA42" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB42" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC42" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD42" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE42" s="62" t="s">
         <v>628</v>
@@ -12786,25 +12839,25 @@
         <v>615</v>
       </c>
       <c r="X43" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y43" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z43" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA43" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB43" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC43" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD43" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE43" s="62" t="s">
         <v>628</v>
@@ -12881,25 +12934,25 @@
         <v>615</v>
       </c>
       <c r="X44" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y44" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z44" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA44" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB44" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC44" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD44" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE44" s="62" t="s">
         <v>628</v>
@@ -12976,25 +13029,25 @@
         <v>615</v>
       </c>
       <c r="X45" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y45" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z45" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA45" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB45" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC45" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD45" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE45" s="62" t="s">
         <v>628</v>
@@ -13071,25 +13124,25 @@
         <v>615</v>
       </c>
       <c r="X46" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y46" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z46" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA46" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB46" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC46" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD46" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE46" s="62" t="s">
         <v>628</v>
@@ -13166,25 +13219,25 @@
         <v>615</v>
       </c>
       <c r="X47" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y47" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z47" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA47" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB47" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC47" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD47" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE47" s="62" t="s">
         <v>628</v>
@@ -13261,25 +13314,25 @@
         <v>615</v>
       </c>
       <c r="X48" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y48" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z48" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA48" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB48" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC48" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD48" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE48" s="62" t="s">
         <v>628</v>
@@ -13356,25 +13409,25 @@
         <v>615</v>
       </c>
       <c r="X49" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y49" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z49" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA49" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB49" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC49" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD49" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE49" s="62" t="s">
         <v>628</v>
@@ -13451,25 +13504,25 @@
         <v>615</v>
       </c>
       <c r="X50" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y50" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z50" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA50" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB50" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC50" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD50" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE50" s="62" t="s">
         <v>628</v>
@@ -13546,25 +13599,25 @@
         <v>615</v>
       </c>
       <c r="X51" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y51" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z51" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA51" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB51" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC51" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD51" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE51" s="62" t="s">
         <v>628</v>
@@ -13641,25 +13694,25 @@
         <v>615</v>
       </c>
       <c r="X52" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y52" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z52" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA52" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB52" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC52" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD52" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE52" s="62" t="s">
         <v>628</v>
@@ -13736,25 +13789,25 @@
         <v>615</v>
       </c>
       <c r="X53" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y53" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z53" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA53" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB53" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC53" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD53" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE53" s="62" t="s">
         <v>628</v>
@@ -13831,25 +13884,25 @@
         <v>615</v>
       </c>
       <c r="X54" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y54" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z54" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA54" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB54" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC54" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD54" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE54" s="62" t="s">
         <v>628</v>
@@ -13926,25 +13979,25 @@
         <v>615</v>
       </c>
       <c r="X55" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y55" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z55" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA55" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB55" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC55" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD55" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE55" s="62" t="s">
         <v>628</v>
@@ -14021,25 +14074,25 @@
         <v>615</v>
       </c>
       <c r="X56" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y56" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z56" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA56" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB56" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC56" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD56" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE56" s="62" t="s">
         <v>628</v>
@@ -14116,25 +14169,25 @@
         <v>615</v>
       </c>
       <c r="X57" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y57" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z57" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA57" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB57" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC57" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD57" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE57" s="62" t="s">
         <v>628</v>
@@ -14211,25 +14264,25 @@
         <v>615</v>
       </c>
       <c r="X58" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y58" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z58" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA58" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB58" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC58" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD58" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE58" s="62" t="s">
         <v>628</v>
@@ -14306,25 +14359,25 @@
         <v>615</v>
       </c>
       <c r="X59" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y59" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z59" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA59" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB59" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC59" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD59" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE59" s="62" t="s">
         <v>628</v>
@@ -14401,25 +14454,25 @@
         <v>615</v>
       </c>
       <c r="X60" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y60" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z60" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA60" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB60" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC60" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD60" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE60" s="62" t="s">
         <v>628</v>
@@ -14496,25 +14549,25 @@
         <v>615</v>
       </c>
       <c r="X61" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y61" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z61" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA61" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB61" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC61" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD61" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE61" s="62" t="s">
         <v>628</v>
@@ -14591,25 +14644,25 @@
         <v>615</v>
       </c>
       <c r="X62" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y62" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z62" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA62" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB62" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC62" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD62" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE62" s="62" t="s">
         <v>628</v>
@@ -14686,25 +14739,25 @@
         <v>615</v>
       </c>
       <c r="X63" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y63" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z63" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA63" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB63" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC63" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD63" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE63" s="62" t="s">
         <v>628</v>
@@ -14781,25 +14834,25 @@
         <v>615</v>
       </c>
       <c r="X64" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y64" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z64" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA64" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB64" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC64" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD64" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE64" s="62" t="s">
         <v>628</v>
@@ -14876,25 +14929,25 @@
         <v>615</v>
       </c>
       <c r="X65" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y65" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z65" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA65" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB65" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC65" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD65" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE65" s="62" t="s">
         <v>628</v>
@@ -14971,25 +15024,25 @@
         <v>615</v>
       </c>
       <c r="X66" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y66" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z66" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA66" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB66" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC66" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD66" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE66" s="62" t="s">
         <v>628</v>
@@ -15066,25 +15119,25 @@
         <v>615</v>
       </c>
       <c r="X67" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y67" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z67" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA67" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB67" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC67" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD67" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE67" s="62" t="s">
         <v>628</v>
@@ -15161,25 +15214,25 @@
         <v>615</v>
       </c>
       <c r="X68" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y68" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z68" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA68" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB68" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC68" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD68" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE68" s="62" t="s">
         <v>628</v>
@@ -15256,25 +15309,25 @@
         <v>615</v>
       </c>
       <c r="X69" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y69" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z69" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA69" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB69" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC69" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD69" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE69" s="62" t="s">
         <v>628</v>
@@ -15351,25 +15404,25 @@
         <v>615</v>
       </c>
       <c r="X70" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y70" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z70" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA70" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB70" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC70" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD70" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE70" s="62" t="s">
         <v>628</v>
@@ -15446,25 +15499,25 @@
         <v>615</v>
       </c>
       <c r="X71" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y71" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z71" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA71" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB71" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC71" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD71" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE71" s="62" t="s">
         <v>628</v>
@@ -15541,25 +15594,25 @@
         <v>615</v>
       </c>
       <c r="X72" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y72" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z72" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA72" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB72" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC72" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD72" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE72" s="62" t="s">
         <v>628</v>
@@ -15636,25 +15689,25 @@
         <v>615</v>
       </c>
       <c r="X73" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y73" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z73" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA73" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB73" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC73" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD73" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE73" s="62" t="s">
         <v>628</v>
@@ -15731,25 +15784,25 @@
         <v>615</v>
       </c>
       <c r="X74" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y74" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z74" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA74" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB74" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC74" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD74" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE74" s="62" t="s">
         <v>628</v>
@@ -15826,25 +15879,25 @@
         <v>615</v>
       </c>
       <c r="X75" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y75" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z75" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA75" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB75" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC75" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD75" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE75" s="62" t="s">
         <v>628</v>
@@ -15921,25 +15974,25 @@
         <v>615</v>
       </c>
       <c r="X76" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y76" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z76" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA76" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB76" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC76" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD76" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE76" s="62" t="s">
         <v>628</v>
@@ -16016,25 +16069,25 @@
         <v>615</v>
       </c>
       <c r="X77" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y77" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z77" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA77" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB77" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC77" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD77" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE77" s="62" t="s">
         <v>628</v>
@@ -16111,25 +16164,25 @@
         <v>615</v>
       </c>
       <c r="X78" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y78" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z78" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA78" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB78" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC78" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD78" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE78" s="62" t="s">
         <v>628</v>
@@ -16206,25 +16259,25 @@
         <v>615</v>
       </c>
       <c r="X79" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y79" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z79" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA79" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB79" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC79" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD79" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE79" s="62" t="s">
         <v>628</v>
@@ -16301,25 +16354,25 @@
         <v>615</v>
       </c>
       <c r="X80" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y80" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z80" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA80" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB80" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC80" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD80" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE80" s="62" t="s">
         <v>628</v>
@@ -16396,25 +16449,25 @@
         <v>615</v>
       </c>
       <c r="X81" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y81" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z81" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA81" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB81" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC81" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD81" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE81" s="62" t="s">
         <v>628</v>
@@ -16491,25 +16544,25 @@
         <v>615</v>
       </c>
       <c r="X82" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y82" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z82" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA82" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB82" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC82" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD82" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE82" s="62" t="s">
         <v>628</v>
@@ -16586,25 +16639,25 @@
         <v>615</v>
       </c>
       <c r="X83" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y83" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z83" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA83" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB83" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC83" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD83" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE83" s="62" t="s">
         <v>628</v>
@@ -16681,25 +16734,25 @@
         <v>615</v>
       </c>
       <c r="X84" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y84" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z84" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA84" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB84" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC84" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD84" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE84" s="62" t="s">
         <v>628</v>
@@ -16776,25 +16829,25 @@
         <v>615</v>
       </c>
       <c r="X85" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y85" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z85" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA85" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB85" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC85" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD85" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE85" s="62" t="s">
         <v>628</v>
@@ -16871,25 +16924,25 @@
         <v>615</v>
       </c>
       <c r="X86" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y86" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z86" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA86" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB86" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC86" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD86" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE86" s="62" t="s">
         <v>628</v>
@@ -16966,25 +17019,25 @@
         <v>615</v>
       </c>
       <c r="X87" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y87" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z87" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA87" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB87" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC87" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD87" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE87" s="62" t="s">
         <v>628</v>
@@ -17061,25 +17114,25 @@
         <v>615</v>
       </c>
       <c r="X88" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y88" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z88" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA88" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB88" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC88" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD88" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE88" s="62" t="s">
         <v>628</v>
@@ -17156,25 +17209,25 @@
         <v>615</v>
       </c>
       <c r="X89" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y89" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z89" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA89" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB89" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC89" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD89" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE89" s="62" t="s">
         <v>628</v>
@@ -17251,25 +17304,25 @@
         <v>615</v>
       </c>
       <c r="X90" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y90" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z90" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA90" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB90" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC90" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD90" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE90" s="62" t="s">
         <v>628</v>
@@ -17346,25 +17399,25 @@
         <v>615</v>
       </c>
       <c r="X91" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y91" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z91" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA91" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB91" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC91" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD91" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE91" s="62" t="s">
         <v>628</v>
@@ -17441,25 +17494,25 @@
         <v>615</v>
       </c>
       <c r="X92" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y92" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z92" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA92" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB92" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC92" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD92" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE92" s="62" t="s">
         <v>628</v>
@@ -17536,25 +17589,25 @@
         <v>615</v>
       </c>
       <c r="X93" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y93" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z93" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA93" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB93" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC93" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD93" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE93" s="62" t="s">
         <v>628</v>
@@ -17631,25 +17684,25 @@
         <v>615</v>
       </c>
       <c r="X94" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y94" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z94" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA94" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB94" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC94" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD94" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE94" s="62" t="s">
         <v>628</v>
@@ -17726,25 +17779,25 @@
         <v>615</v>
       </c>
       <c r="X95" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y95" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z95" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA95" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB95" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC95" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD95" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE95" s="62" t="s">
         <v>628</v>
@@ -17821,25 +17874,25 @@
         <v>615</v>
       </c>
       <c r="X96" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y96" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z96" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA96" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB96" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC96" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD96" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE96" s="62" t="s">
         <v>628</v>
@@ -17916,25 +17969,25 @@
         <v>615</v>
       </c>
       <c r="X97" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y97" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z97" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA97" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB97" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC97" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD97" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE97" s="62" t="s">
         <v>628</v>
@@ -18011,25 +18064,25 @@
         <v>615</v>
       </c>
       <c r="X98" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y98" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z98" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA98" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB98" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC98" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD98" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE98" s="62" t="s">
         <v>628</v>
@@ -18106,25 +18159,25 @@
         <v>615</v>
       </c>
       <c r="X99" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y99" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z99" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA99" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB99" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC99" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD99" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE99" s="62" t="s">
         <v>628</v>
@@ -18201,25 +18254,25 @@
         <v>615</v>
       </c>
       <c r="X100" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y100" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z100" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA100" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB100" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC100" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD100" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE100" s="62" t="s">
         <v>628</v>
@@ -18296,25 +18349,25 @@
         <v>615</v>
       </c>
       <c r="X101" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y101" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z101" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA101" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB101" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC101" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD101" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE101" s="62" t="s">
         <v>628</v>
@@ -18391,25 +18444,25 @@
         <v>615</v>
       </c>
       <c r="X102" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y102" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z102" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA102" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB102" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC102" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD102" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE102" s="62" t="s">
         <v>628</v>
@@ -18486,25 +18539,25 @@
         <v>615</v>
       </c>
       <c r="X103" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y103" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z103" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA103" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB103" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC103" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD103" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE103" s="62" t="s">
         <v>628</v>
@@ -18581,25 +18634,25 @@
         <v>615</v>
       </c>
       <c r="X104" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y104" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z104" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA104" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB104" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC104" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD104" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE104" s="62" t="s">
         <v>628</v>
@@ -18676,25 +18729,25 @@
         <v>615</v>
       </c>
       <c r="X105" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y105" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z105" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA105" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB105" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC105" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD105" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE105" s="62" t="s">
         <v>628</v>
@@ -18771,25 +18824,25 @@
         <v>615</v>
       </c>
       <c r="X106" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y106" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z106" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA106" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB106" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC106" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD106" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE106" s="62" t="s">
         <v>628</v>
@@ -18866,25 +18919,25 @@
         <v>615</v>
       </c>
       <c r="X107" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y107" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z107" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA107" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB107" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC107" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD107" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE107" s="62" t="s">
         <v>628</v>
@@ -18961,25 +19014,25 @@
         <v>615</v>
       </c>
       <c r="X108" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y108" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z108" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA108" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB108" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC108" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD108" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE108" s="62" t="s">
         <v>628</v>
@@ -19056,25 +19109,25 @@
         <v>615</v>
       </c>
       <c r="X109" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y109" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z109" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA109" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB109" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC109" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD109" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE109" s="62" t="s">
         <v>628</v>
@@ -19151,25 +19204,25 @@
         <v>615</v>
       </c>
       <c r="X110" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y110" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z110" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA110" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB110" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC110" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD110" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE110" s="62" t="s">
         <v>628</v>
@@ -19246,25 +19299,25 @@
         <v>615</v>
       </c>
       <c r="X111" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y111" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z111" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA111" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB111" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC111" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD111" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE111" s="62" t="s">
         <v>628</v>
@@ -19341,25 +19394,25 @@
         <v>615</v>
       </c>
       <c r="X112" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y112" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z112" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA112" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB112" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC112" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD112" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE112" s="62" t="s">
         <v>628</v>
@@ -19436,25 +19489,25 @@
         <v>615</v>
       </c>
       <c r="X113" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y113" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z113" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA113" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB113" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC113" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD113" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE113" s="62" t="s">
         <v>628</v>
@@ -19531,25 +19584,25 @@
         <v>615</v>
       </c>
       <c r="X114" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y114" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z114" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA114" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB114" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC114" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD114" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE114" s="62" t="s">
         <v>628</v>
@@ -19626,25 +19679,25 @@
         <v>615</v>
       </c>
       <c r="X115" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y115" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z115" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA115" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB115" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC115" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD115" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE115" s="62" t="s">
         <v>628</v>
@@ -19721,25 +19774,25 @@
         <v>615</v>
       </c>
       <c r="X116" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y116" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z116" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA116" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB116" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC116" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD116" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE116" s="62" t="s">
         <v>628</v>
@@ -19816,25 +19869,25 @@
         <v>615</v>
       </c>
       <c r="X117" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y117" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z117" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA117" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB117" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC117" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD117" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE117" s="62" t="s">
         <v>628</v>
@@ -19911,25 +19964,25 @@
         <v>615</v>
       </c>
       <c r="X118" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y118" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z118" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA118" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB118" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC118" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD118" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE118" s="62" t="s">
         <v>628</v>
@@ -20006,25 +20059,25 @@
         <v>615</v>
       </c>
       <c r="X119" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y119" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z119" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA119" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB119" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC119" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD119" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE119" s="62" t="s">
         <v>628</v>
@@ -20101,25 +20154,25 @@
         <v>615</v>
       </c>
       <c r="X120" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y120" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z120" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA120" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB120" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC120" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD120" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE120" s="62" t="s">
         <v>628</v>
@@ -20196,25 +20249,25 @@
         <v>615</v>
       </c>
       <c r="X121" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y121" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z121" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA121" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB121" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC121" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD121" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE121" s="62" t="s">
         <v>628</v>
@@ -20291,25 +20344,25 @@
         <v>615</v>
       </c>
       <c r="X122" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y122" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z122" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA122" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB122" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC122" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD122" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE122" s="62" t="s">
         <v>628</v>
@@ -20386,25 +20439,25 @@
         <v>615</v>
       </c>
       <c r="X123" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y123" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z123" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA123" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB123" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC123" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD123" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE123" s="62" t="s">
         <v>628</v>
@@ -20481,25 +20534,25 @@
         <v>615</v>
       </c>
       <c r="X124" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y124" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z124" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA124" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB124" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC124" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD124" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE124" s="62" t="s">
         <v>628</v>
@@ -20576,25 +20629,25 @@
         <v>615</v>
       </c>
       <c r="X125" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y125" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z125" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA125" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB125" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC125" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD125" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE125" s="62" t="s">
         <v>628</v>
@@ -20671,25 +20724,25 @@
         <v>615</v>
       </c>
       <c r="X126" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y126" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z126" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA126" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB126" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC126" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD126" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE126" s="62" t="s">
         <v>628</v>
@@ -20766,25 +20819,25 @@
         <v>615</v>
       </c>
       <c r="X127" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y127" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z127" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA127" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB127" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC127" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD127" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE127" s="62" t="s">
         <v>628</v>
@@ -20861,25 +20914,25 @@
         <v>615</v>
       </c>
       <c r="X128" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y128" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z128" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA128" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB128" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC128" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD128" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE128" s="62" t="s">
         <v>628</v>
@@ -20956,25 +21009,25 @@
         <v>615</v>
       </c>
       <c r="X129" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y129" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z129" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA129" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB129" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC129" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD129" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE129" s="62" t="s">
         <v>628</v>
@@ -21051,25 +21104,25 @@
         <v>615</v>
       </c>
       <c r="X130" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y130" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z130" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA130" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB130" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC130" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD130" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE130" s="62" t="s">
         <v>628</v>
@@ -21146,25 +21199,25 @@
         <v>615</v>
       </c>
       <c r="X131" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y131" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z131" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA131" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB131" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC131" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD131" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE131" s="62" t="s">
         <v>628</v>
@@ -21241,25 +21294,25 @@
         <v>615</v>
       </c>
       <c r="X132" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y132" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z132" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA132" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB132" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC132" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD132" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE132" s="62" t="s">
         <v>628</v>
@@ -21336,25 +21389,25 @@
         <v>615</v>
       </c>
       <c r="X133" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y133" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z133" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA133" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB133" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC133" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD133" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE133" s="62" t="s">
         <v>628</v>
@@ -21431,25 +21484,25 @@
         <v>615</v>
       </c>
       <c r="X134" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y134" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z134" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA134" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB134" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC134" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD134" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE134" s="62" t="s">
         <v>628</v>
@@ -21526,25 +21579,25 @@
         <v>615</v>
       </c>
       <c r="X135" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y135" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z135" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA135" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB135" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC135" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD135" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE135" s="62" t="s">
         <v>628</v>
@@ -21621,25 +21674,25 @@
         <v>615</v>
       </c>
       <c r="X136" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y136" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z136" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA136" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB136" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC136" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD136" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE136" s="62" t="s">
         <v>628</v>
@@ -21716,25 +21769,25 @@
         <v>615</v>
       </c>
       <c r="X137" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y137" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z137" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA137" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB137" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC137" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD137" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE137" s="62" t="s">
         <v>628</v>
@@ -21811,25 +21864,25 @@
         <v>615</v>
       </c>
       <c r="X138" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y138" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z138" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA138" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB138" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC138" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD138" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE138" s="62" t="s">
         <v>628</v>
@@ -21906,25 +21959,25 @@
         <v>615</v>
       </c>
       <c r="X139" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y139" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z139" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA139" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB139" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC139" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD139" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE139" s="62" t="s">
         <v>628</v>
@@ -22001,25 +22054,25 @@
         <v>615</v>
       </c>
       <c r="X140" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y140" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z140" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA140" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB140" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC140" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD140" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE140" s="62" t="s">
         <v>628</v>
@@ -22096,25 +22149,25 @@
         <v>615</v>
       </c>
       <c r="X141" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y141" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z141" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA141" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB141" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC141" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD141" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE141" s="62" t="s">
         <v>628</v>
@@ -22191,25 +22244,25 @@
         <v>615</v>
       </c>
       <c r="X142" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y142" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z142" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA142" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB142" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC142" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD142" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE142" s="62" t="s">
         <v>628</v>
@@ -22286,25 +22339,25 @@
         <v>615</v>
       </c>
       <c r="X143" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y143" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z143" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA143" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB143" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC143" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD143" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE143" s="62" t="s">
         <v>628</v>
@@ -22381,25 +22434,25 @@
         <v>615</v>
       </c>
       <c r="X144" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y144" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z144" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA144" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB144" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC144" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD144" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE144" s="62" t="s">
         <v>628</v>
@@ -22476,25 +22529,25 @@
         <v>615</v>
       </c>
       <c r="X145" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y145" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z145" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA145" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB145" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC145" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD145" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE145" s="62" t="s">
         <v>628</v>
@@ -22571,25 +22624,25 @@
         <v>615</v>
       </c>
       <c r="X146" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y146" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z146" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA146" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB146" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC146" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD146" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE146" s="62" t="s">
         <v>628</v>
@@ -22666,25 +22719,25 @@
         <v>615</v>
       </c>
       <c r="X147" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y147" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z147" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA147" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB147" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC147" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD147" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE147" s="62" t="s">
         <v>628</v>
@@ -22761,25 +22814,25 @@
         <v>615</v>
       </c>
       <c r="X148" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y148" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z148" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA148" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB148" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC148" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD148" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE148" s="62" t="s">
         <v>628</v>
@@ -22856,25 +22909,25 @@
         <v>615</v>
       </c>
       <c r="X149" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y149" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z149" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA149" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB149" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC149" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD149" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE149" s="62" t="s">
         <v>628</v>
@@ -22951,25 +23004,25 @@
         <v>615</v>
       </c>
       <c r="X150" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y150" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z150" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA150" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB150" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC150" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD150" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE150" s="62" t="s">
         <v>628</v>
@@ -23046,25 +23099,25 @@
         <v>615</v>
       </c>
       <c r="X151" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y151" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z151" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA151" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB151" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC151" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD151" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE151" s="62" t="s">
         <v>628</v>
@@ -23141,25 +23194,25 @@
         <v>615</v>
       </c>
       <c r="X152" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y152" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z152" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA152" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB152" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC152" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD152" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE152" s="62" t="s">
         <v>628</v>
@@ -23236,25 +23289,25 @@
         <v>615</v>
       </c>
       <c r="X153" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y153" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z153" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA153" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB153" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC153" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD153" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE153" s="62" t="s">
         <v>628</v>
@@ -23331,25 +23384,25 @@
         <v>615</v>
       </c>
       <c r="X154" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y154" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z154" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA154" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB154" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC154" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD154" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE154" s="62" t="s">
         <v>628</v>
@@ -23426,25 +23479,25 @@
         <v>615</v>
       </c>
       <c r="X155" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y155" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z155" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA155" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB155" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC155" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD155" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE155" s="62" t="s">
         <v>628</v>
@@ -23521,25 +23574,25 @@
         <v>615</v>
       </c>
       <c r="X156" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y156" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z156" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA156" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB156" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC156" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD156" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE156" s="62" t="s">
         <v>628</v>
@@ -23616,25 +23669,25 @@
         <v>615</v>
       </c>
       <c r="X157" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y157" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z157" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA157" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB157" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC157" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD157" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE157" s="62" t="s">
         <v>628</v>
@@ -23711,25 +23764,25 @@
         <v>615</v>
       </c>
       <c r="X158" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y158" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z158" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA158" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB158" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC158" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD158" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE158" s="62" t="s">
         <v>628</v>
@@ -23806,25 +23859,25 @@
         <v>615</v>
       </c>
       <c r="X159" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y159" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z159" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA159" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB159" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC159" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD159" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE159" s="62" t="s">
         <v>628</v>
@@ -23901,25 +23954,25 @@
         <v>615</v>
       </c>
       <c r="X160" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y160" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z160" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA160" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB160" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC160" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD160" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE160" s="62" t="s">
         <v>628</v>
@@ -23996,25 +24049,25 @@
         <v>615</v>
       </c>
       <c r="X161" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y161" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z161" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA161" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB161" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC161" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD161" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE161" s="62" t="s">
         <v>628</v>
@@ -24091,25 +24144,25 @@
         <v>615</v>
       </c>
       <c r="X162" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y162" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z162" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA162" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB162" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC162" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD162" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE162" s="62" t="s">
         <v>628</v>
@@ -24186,25 +24239,25 @@
         <v>615</v>
       </c>
       <c r="X163" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y163" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z163" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA163" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB163" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC163" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD163" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE163" s="62" t="s">
         <v>628</v>
@@ -24281,25 +24334,25 @@
         <v>615</v>
       </c>
       <c r="X164" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y164" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z164" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA164" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB164" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC164" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD164" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE164" s="62" t="s">
         <v>628</v>
@@ -24376,25 +24429,25 @@
         <v>615</v>
       </c>
       <c r="X165" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y165" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z165" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA165" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB165" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC165" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD165" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE165" s="62" t="s">
         <v>628</v>
@@ -24471,25 +24524,25 @@
         <v>615</v>
       </c>
       <c r="X166" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y166" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z166" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA166" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB166" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC166" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD166" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE166" s="62" t="s">
         <v>628</v>
@@ -24566,25 +24619,25 @@
         <v>615</v>
       </c>
       <c r="X167" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y167" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z167" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA167" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB167" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC167" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD167" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE167" s="62" t="s">
         <v>628</v>
@@ -24661,25 +24714,25 @@
         <v>615</v>
       </c>
       <c r="X168" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y168" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z168" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA168" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB168" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC168" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD168" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE168" s="62" t="s">
         <v>628</v>
@@ -24756,25 +24809,25 @@
         <v>615</v>
       </c>
       <c r="X169" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y169" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z169" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA169" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB169" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC169" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD169" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE169" s="62" t="s">
         <v>628</v>
@@ -24826,11 +24879,12 @@
       <c r="O170" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="P170" s="81" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q170" s="39" t="s">
-        <v>191</v>
+      <c r="P170" s="83" t="str">
+        <f t="shared" ref="P170:P174" si="0">IF(Q170="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="Q170" s="84" t="s">
+        <v>632</v>
       </c>
       <c r="R170" s="81" t="s">
         <v>191</v>
@@ -24851,25 +24905,25 @@
         <v>615</v>
       </c>
       <c r="X170" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y170" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z170" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA170" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB170" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC170" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD170" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE170" s="62" t="s">
         <v>628</v>
@@ -24921,11 +24975,12 @@
       <c r="O171" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="P171" s="81" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q171" s="39" t="s">
-        <v>191</v>
+      <c r="P171" s="83" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q171" s="84" t="s">
+        <v>633</v>
       </c>
       <c r="R171" s="81" t="s">
         <v>191</v>
@@ -24946,25 +25001,25 @@
         <v>615</v>
       </c>
       <c r="X171" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y171" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z171" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA171" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB171" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC171" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD171" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE171" s="62" t="s">
         <v>628</v>
@@ -25016,11 +25071,12 @@
       <c r="O172" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="P172" s="81" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q172" s="39" t="s">
-        <v>191</v>
+      <c r="P172" s="83" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q172" s="84" t="s">
+        <v>634</v>
       </c>
       <c r="R172" s="81" t="s">
         <v>191</v>
@@ -25041,25 +25097,25 @@
         <v>615</v>
       </c>
       <c r="X172" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y172" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z172" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA172" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB172" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC172" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD172" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE172" s="62" t="s">
         <v>628</v>
@@ -25111,11 +25167,12 @@
       <c r="O173" s="13" t="s">
         <v>627</v>
       </c>
-      <c r="P173" s="81" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q173" s="39" t="s">
-        <v>191</v>
+      <c r="P173" s="83" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q173" s="84" t="s">
+        <v>635</v>
       </c>
       <c r="R173" s="81" t="s">
         <v>191</v>
@@ -25136,25 +25193,25 @@
         <v>615</v>
       </c>
       <c r="X173" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y173" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z173" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA173" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB173" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC173" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD173" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE173" s="62" t="s">
         <v>628</v>
@@ -25206,11 +25263,12 @@
       <c r="O174" s="19" t="s">
         <v>630</v>
       </c>
-      <c r="P174" s="82" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q174" s="79" t="s">
-        <v>191</v>
+      <c r="P174" s="83" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q174" s="84" t="s">
+        <v>636</v>
       </c>
       <c r="R174" s="82" t="s">
         <v>191</v>
@@ -25231,25 +25289,25 @@
         <v>615</v>
       </c>
       <c r="X174" s="61" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Y174" s="62" t="s">
         <v>619</v>
       </c>
       <c r="Z174" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AA174" s="62" t="s">
         <v>622</v>
       </c>
       <c r="AB174" s="61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC174" s="62" t="s">
         <v>625</v>
       </c>
       <c r="AD174" s="61" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AE174" s="62" t="s">
         <v>628</v>
@@ -25258,149 +25316,164 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B169 B175:B1048576">
-    <cfRule type="duplicateValues" dxfId="30" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170:B174">
-    <cfRule type="duplicateValues" dxfId="29" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="27" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="51" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E170:E174">
-    <cfRule type="cellIs" dxfId="26" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="27" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="25" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F170:F174">
-    <cfRule type="cellIs" dxfId="24" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G170:G174">
-    <cfRule type="cellIs" dxfId="23" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="22" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="62" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H170:H174">
-    <cfRule type="cellIs" dxfId="21" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I170:I174">
-    <cfRule type="cellIs" dxfId="20" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="19" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="61" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="18" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="17" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="67" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="16" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="59" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P170:U174">
-    <cfRule type="cellIs" dxfId="15" priority="38" operator="equal">
+  <conditionalFormatting sqref="R170:U174">
+    <cfRule type="cellIs" dxfId="18" priority="48" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="14" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="13" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="57" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:U169">
-    <cfRule type="cellIs" dxfId="12" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="54" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:AE1 D170:D174 T175:AE1048576">
-    <cfRule type="cellIs" dxfId="11" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="10" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:W174">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="8" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y3">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+  <conditionalFormatting sqref="X2:X174">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X4:AE174">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+  <conditionalFormatting sqref="Y2:Y174">
+    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="5" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:AA3">
+  <conditionalFormatting sqref="Z2:Z174">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA174">
+    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB1">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AB174">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="3" priority="24" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AC3">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+  <conditionalFormatting sqref="AC2:AC174">
+    <cfRule type="cellIs" dxfId="3" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="1" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AE3">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+  <conditionalFormatting sqref="AD2:AD174">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE2:AE174">
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34E0B03-B7FA-487E-9A82-0A0D093A3477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04B8E18-DC73-4D59-B3D5-18814A591180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -1989,19 +1989,19 @@
     <t>é.selecionado.por</t>
   </si>
   <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
-  </si>
-  <si>
-    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
-  </si>
-  <si>
-    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
   </si>
 </sst>
 </file>
@@ -2797,7 +2797,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2805,7 +2805,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -5800,14 +5800,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B000FC7-022F-4B0D-BBFB-289DF5E27855}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>177</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>178</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5851,7 +5851,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="43" t="s">
         <v>9</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>179</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>181</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>182</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>183</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>184</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>185</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>186</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -5996,19 +5996,19 @@
         <v>432</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>187</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46257.755699652778</v>
+        <v>46258.542576967593</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>443</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43" t="s">
         <v>436</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="43" t="s">
         <v>444</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>176</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>188</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>195</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>197</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="43" t="s">
         <v>428</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="43" t="s">
         <v>548</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="43" t="s">
         <v>550</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="43" t="s">
         <v>552</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="43" t="s">
         <v>554</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="43" t="s">
         <v>556</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="43" t="s">
         <v>558</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="43" t="s">
         <v>560</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="43" t="s">
         <v>562</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="43" t="s">
         <v>564</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="43" t="s">
         <v>566</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="43" t="s">
         <v>568</v>
       </c>
@@ -6219,7 +6219,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>570</v>
       </c>
@@ -6230,7 +6230,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="72" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="72" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="43" t="s">
         <v>572</v>
       </c>
@@ -6257,35 +6257,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75533AB-3BC5-4EED-85BC-780B8F4A6EA8}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC23"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.19921875" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.796875" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="33" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="60" customWidth="1"/>
     <col min="17" max="17" width="63.5" customWidth="1"/>
     <col min="18" max="18" width="53.5" customWidth="1"/>
     <col min="19" max="19" width="5" style="33" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.796875" style="33" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="43.796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.83203125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="35.296875" customWidth="1"/>
+    <col min="27" max="27" width="35.33203125" customWidth="1"/>
     <col min="28" max="29" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="30.9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="57.75" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>374</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="55">
         <v>2</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="55">
         <v>3</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="55">
         <v>4</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="55">
         <v>5</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="55">
         <v>6</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="55">
         <v>7</v>
       </c>
@@ -6956,7 +6956,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="55">
         <v>8</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="55">
         <v>9</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="55">
         <v>10</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="55">
         <v>11</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="55">
         <v>12</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="55">
         <v>13</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="55">
         <v>14</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="55">
         <v>15</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="55">
         <v>16</v>
       </c>
@@ -7829,7 +7829,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="55">
         <v>17</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="55">
         <v>18</v>
       </c>
@@ -8023,7 +8023,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="55">
         <v>19</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="55">
         <v>20</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="55">
         <v>21</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="55">
         <v>22</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="55">
         <v>23</v>
       </c>
@@ -8547,13 +8547,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A4D5B2-E607-43E1-969D-E9BC12588F0D}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
         <v>375</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -8700,13 +8700,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50BE4DF8-DB25-47BD-BFAE-132A16409236}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.796875" customWidth="1"/>
+    <col min="2" max="3" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8742,43 +8742,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AE174"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.69921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.59765625" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.09765625" style="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.19921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.09765625" style="38" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.3984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.69921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.296875" style="38" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.296875" style="38" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.3984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="79.3984375" style="38" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.33203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="54.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" style="38" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" style="38" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.8984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.83203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" style="2" customWidth="1"/>
-    <col min="23" max="23" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11" style="2" customWidth="1"/>
     <col min="25" max="25" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11" style="2" customWidth="1"/>
-    <col min="27" max="27" width="7.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" style="2" customWidth="1"/>
-    <col min="29" max="29" width="7.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" style="2" customWidth="1"/>
     <col min="31" max="31" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="32" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>189</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -8968,7 +8968,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -10108,7 +10108,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>16</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>17</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>18</v>
       </c>
@@ -10488,7 +10488,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>19</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>20</v>
       </c>
@@ -10678,7 +10678,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>21</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>22</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>23</v>
       </c>
@@ -10963,7 +10963,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>24</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>25</v>
       </c>
@@ -11153,7 +11153,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>26</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>27</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>28</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>29</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>30</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>31</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>32</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>33</v>
       </c>
@@ -11913,7 +11913,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>34</v>
       </c>
@@ -12008,7 +12008,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>35</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>36</v>
       </c>
@@ -12198,7 +12198,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>37</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>38</v>
       </c>
@@ -12388,7 +12388,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>39</v>
       </c>
@@ -12483,7 +12483,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>40</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>41</v>
       </c>
@@ -12673,7 +12673,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>42</v>
       </c>
@@ -12768,7 +12768,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>43</v>
       </c>
@@ -12863,7 +12863,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>44</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>45</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>46</v>
       </c>
@@ -13148,7 +13148,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>47</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>48</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>49</v>
       </c>
@@ -13433,7 +13433,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>50</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>51</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>52</v>
       </c>
@@ -13718,7 +13718,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>53</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>54</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>55</v>
       </c>
@@ -14003,7 +14003,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>56</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>57</v>
       </c>
@@ -14193,7 +14193,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>58</v>
       </c>
@@ -14288,7 +14288,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>59</v>
       </c>
@@ -14383,7 +14383,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>60</v>
       </c>
@@ -14478,7 +14478,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>61</v>
       </c>
@@ -14573,7 +14573,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="62" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>62</v>
       </c>
@@ -14668,7 +14668,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="63" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>63</v>
       </c>
@@ -14763,7 +14763,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>64</v>
       </c>
@@ -14858,7 +14858,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>65</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>66</v>
       </c>
@@ -15048,7 +15048,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>67</v>
       </c>
@@ -15143,7 +15143,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>68</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>69</v>
       </c>
@@ -15333,7 +15333,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>70</v>
       </c>
@@ -15428,7 +15428,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="8">
         <v>71</v>
       </c>
@@ -15523,7 +15523,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>72</v>
       </c>
@@ -15618,7 +15618,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="8">
         <v>73</v>
       </c>
@@ -15713,7 +15713,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="8">
         <v>74</v>
       </c>
@@ -15808,7 +15808,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>75</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="8">
         <v>76</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="8">
         <v>77</v>
       </c>
@@ -16093,7 +16093,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="8">
         <v>78</v>
       </c>
@@ -16188,7 +16188,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="8">
         <v>79</v>
       </c>
@@ -16283,7 +16283,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="8">
         <v>80</v>
       </c>
@@ -16378,7 +16378,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="81" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="8">
         <v>81</v>
       </c>
@@ -16473,7 +16473,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="82" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="8">
         <v>82</v>
       </c>
@@ -16568,7 +16568,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="83" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="8">
         <v>83</v>
       </c>
@@ -16663,7 +16663,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="84" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="8">
         <v>84</v>
       </c>
@@ -16758,7 +16758,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="85" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="8">
         <v>85</v>
       </c>
@@ -16853,7 +16853,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="86" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="8">
         <v>86</v>
       </c>
@@ -16948,7 +16948,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="87" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="8">
         <v>87</v>
       </c>
@@ -17043,7 +17043,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="88" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="8">
         <v>88</v>
       </c>
@@ -17138,7 +17138,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="89" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
         <v>89</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="90" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
         <v>90</v>
       </c>
@@ -17328,7 +17328,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="91" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
         <v>91</v>
       </c>
@@ -17423,7 +17423,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="92" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="8">
         <v>92</v>
       </c>
@@ -17518,7 +17518,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="93" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="8">
         <v>93</v>
       </c>
@@ -17613,7 +17613,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="94" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="8">
         <v>94</v>
       </c>
@@ -17708,7 +17708,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="95" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="8">
         <v>95</v>
       </c>
@@ -17803,7 +17803,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="96" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="8">
         <v>96</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="97" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="8">
         <v>97</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="98" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="8">
         <v>98</v>
       </c>
@@ -18088,7 +18088,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="99" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="8">
         <v>99</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="100" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="8">
         <v>100</v>
       </c>
@@ -18278,7 +18278,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="101" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="8">
         <v>101</v>
       </c>
@@ -18373,7 +18373,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="102" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="8">
         <v>102</v>
       </c>
@@ -18468,7 +18468,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="103" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="8">
         <v>103</v>
       </c>
@@ -18563,7 +18563,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="104" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="8">
         <v>104</v>
       </c>
@@ -18658,7 +18658,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="105" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="8">
         <v>105</v>
       </c>
@@ -18753,7 +18753,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="106" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="8">
         <v>106</v>
       </c>
@@ -18848,7 +18848,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="107" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="8">
         <v>107</v>
       </c>
@@ -18943,7 +18943,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="108" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="8">
         <v>108</v>
       </c>
@@ -19038,7 +19038,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="109" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="8">
         <v>109</v>
       </c>
@@ -19133,7 +19133,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="110" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="8">
         <v>110</v>
       </c>
@@ -19228,7 +19228,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="111" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="8">
         <v>111</v>
       </c>
@@ -19323,7 +19323,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="112" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="8">
         <v>112</v>
       </c>
@@ -19418,7 +19418,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="113" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="8">
         <v>113</v>
       </c>
@@ -19513,7 +19513,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="114" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="8">
         <v>114</v>
       </c>
@@ -19608,7 +19608,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="115" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="8">
         <v>115</v>
       </c>
@@ -19703,7 +19703,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="116" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="8">
         <v>116</v>
       </c>
@@ -19798,7 +19798,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="117" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="8">
         <v>117</v>
       </c>
@@ -19893,7 +19893,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="118" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="8">
         <v>118</v>
       </c>
@@ -19988,7 +19988,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="119" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="8">
         <v>119</v>
       </c>
@@ -20083,7 +20083,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="120" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="8">
         <v>120</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="121" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="8">
         <v>121</v>
       </c>
@@ -20273,7 +20273,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="122" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="8">
         <v>122</v>
       </c>
@@ -20368,7 +20368,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="123" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="8">
         <v>123</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="124" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="8">
         <v>124</v>
       </c>
@@ -20558,7 +20558,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="125" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="8">
         <v>125</v>
       </c>
@@ -20653,7 +20653,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="126" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="8">
         <v>126</v>
       </c>
@@ -20748,7 +20748,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="127" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="8">
         <v>127</v>
       </c>
@@ -20843,7 +20843,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="128" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="8">
         <v>128</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="129" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="8">
         <v>129</v>
       </c>
@@ -21033,7 +21033,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="8">
         <v>130</v>
       </c>
@@ -21128,7 +21128,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="8">
         <v>131</v>
       </c>
@@ -21223,7 +21223,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
         <v>132</v>
       </c>
@@ -21318,7 +21318,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <v>133</v>
       </c>
@@ -21413,7 +21413,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="134" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <v>134</v>
       </c>
@@ -21508,7 +21508,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <v>135</v>
       </c>
@@ -21603,7 +21603,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <v>136</v>
       </c>
@@ -21698,7 +21698,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="137" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <v>137</v>
       </c>
@@ -21793,7 +21793,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="138" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <v>138</v>
       </c>
@@ -21888,7 +21888,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="139" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="8">
         <v>139</v>
       </c>
@@ -21983,7 +21983,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="8">
         <v>140</v>
       </c>
@@ -22078,7 +22078,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="8">
         <v>141</v>
       </c>
@@ -22173,7 +22173,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="8">
         <v>142</v>
       </c>
@@ -22268,7 +22268,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="8">
         <v>143</v>
       </c>
@@ -22363,7 +22363,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="8">
         <v>144</v>
       </c>
@@ -22458,7 +22458,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="8">
         <v>145</v>
       </c>
@@ -22553,7 +22553,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
         <v>146</v>
       </c>
@@ -22648,7 +22648,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <v>147</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <v>148</v>
       </c>
@@ -22838,7 +22838,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <v>149</v>
       </c>
@@ -22933,7 +22933,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <v>150</v>
       </c>
@@ -23028,7 +23028,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <v>151</v>
       </c>
@@ -23123,7 +23123,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <v>152</v>
       </c>
@@ -23218,7 +23218,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <v>153</v>
       </c>
@@ -23313,7 +23313,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <v>154</v>
       </c>
@@ -23408,7 +23408,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <v>155</v>
       </c>
@@ -23503,7 +23503,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <v>156</v>
       </c>
@@ -23598,7 +23598,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <v>157</v>
       </c>
@@ -23693,7 +23693,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <v>158</v>
       </c>
@@ -23788,7 +23788,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <v>159</v>
       </c>
@@ -23883,7 +23883,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <v>160</v>
       </c>
@@ -23978,7 +23978,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="161" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <v>161</v>
       </c>
@@ -24073,7 +24073,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="162" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <v>162</v>
       </c>
@@ -24168,7 +24168,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="163" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <v>163</v>
       </c>
@@ -24263,7 +24263,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="164" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <v>164</v>
       </c>
@@ -24358,7 +24358,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="165" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="8">
         <v>165</v>
       </c>
@@ -24453,7 +24453,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="166" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="8">
         <v>166</v>
       </c>
@@ -24548,7 +24548,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="167" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
         <v>166</v>
       </c>
@@ -24643,7 +24643,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="168" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
         <v>166</v>
       </c>
@@ -24738,7 +24738,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="169" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
         <v>166</v>
       </c>
@@ -24833,7 +24833,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="170" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="8">
         <v>167</v>
       </c>
@@ -24929,7 +24929,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="171" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="8">
         <v>168</v>
       </c>
@@ -25025,7 +25025,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="172" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="8">
         <v>169</v>
       </c>
@@ -25121,7 +25121,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="173" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="8">
         <v>170</v>
       </c>
@@ -25217,7 +25217,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="174" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="8">
         <v>171</v>
       </c>
@@ -25382,13 +25382,13 @@
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R170:U174">
-    <cfRule type="cellIs" dxfId="18" priority="48" operator="equal">
+  <conditionalFormatting sqref="R1">
+    <cfRule type="cellIs" dxfId="18" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="17" priority="58" operator="equal">
+  <conditionalFormatting sqref="R170:U174">
+    <cfRule type="cellIs" dxfId="17" priority="48" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04B8E18-DC73-4D59-B3D5-18814A591180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87314241-98D4-4C20-9C13-3F3C14E7A6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -5800,14 +5800,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B000FC7-022F-4B0D-BBFB-289DF5E27855}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>177</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>178</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5851,7 +5851,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="43" t="s">
         <v>9</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>179</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>181</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>182</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>183</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>184</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>185</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>186</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -5996,19 +5996,19 @@
         <v>432</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>187</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46258.542576967593</v>
+        <v>46264.561405324072</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>443</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="43" t="s">
         <v>436</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="43" t="s">
         <v>444</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>176</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>188</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>195</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>197</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="47" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" s="47" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="43" t="s">
         <v>428</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="43" t="s">
         <v>548</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="43" t="s">
         <v>550</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="43" t="s">
         <v>552</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="43" t="s">
         <v>554</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="43" t="s">
         <v>556</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="43" t="s">
         <v>558</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="43" t="s">
         <v>560</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="43" t="s">
         <v>562</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="43" t="s">
         <v>564</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="43" t="s">
         <v>566</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="43" t="s">
         <v>568</v>
       </c>
@@ -6219,7 +6219,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>570</v>
       </c>
@@ -6230,7 +6230,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="72" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="72" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="43" t="s">
         <v>572</v>
       </c>
@@ -6257,35 +6257,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75533AB-3BC5-4EED-85BC-780B8F4A6EA8}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC23"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.296875" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.19921875" style="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.796875" style="33" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.796875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="60" customWidth="1"/>
     <col min="17" max="17" width="63.5" customWidth="1"/>
     <col min="18" max="18" width="53.5" customWidth="1"/>
     <col min="19" max="19" width="5" style="33" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.796875" style="33" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.796875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="35.33203125" customWidth="1"/>
+    <col min="27" max="27" width="35.296875" customWidth="1"/>
     <col min="28" max="29" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>374</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="55">
         <v>2</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="55">
         <v>3</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="55">
         <v>4</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="55">
         <v>5</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="55">
         <v>6</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="55">
         <v>7</v>
       </c>
@@ -6956,7 +6956,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="55">
         <v>8</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="55">
         <v>9</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="55">
         <v>10</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="55">
         <v>11</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="55">
         <v>12</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="55">
         <v>13</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="55">
         <v>14</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="55">
         <v>15</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="55">
         <v>16</v>
       </c>
@@ -7829,7 +7829,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="55">
         <v>17</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="55">
         <v>18</v>
       </c>
@@ -8023,7 +8023,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="55">
         <v>19</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="55">
         <v>20</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="55">
         <v>21</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="55">
         <v>22</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="55">
         <v>23</v>
       </c>
@@ -8422,10 +8422,10 @@
         <v>608</v>
       </c>
       <c r="D23" s="32" t="s">
+        <v>610</v>
+      </c>
+      <c r="E23" s="32" t="s">
         <v>609</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>610</v>
       </c>
       <c r="F23" s="32" t="s">
         <v>611</v>
@@ -8451,11 +8451,11 @@
       </c>
       <c r="M23" s="58" t="str">
         <f t="shared" si="9"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N23" s="58" t="str">
         <f t="shared" si="9"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O23" s="58" t="str">
         <f t="shared" si="9"/>
@@ -8479,11 +8479,11 @@
       </c>
       <c r="U23" s="42" t="str">
         <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V23" s="59" t="str">
         <f t="shared" si="10"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W23" s="42" t="s">
         <v>445</v>
@@ -8547,13 +8547,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A4D5B2-E607-43E1-969D-E9BC12588F0D}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>375</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -8700,13 +8700,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50BE4DF8-DB25-47BD-BFAE-132A16409236}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.83203125" customWidth="1"/>
+    <col min="2" max="3" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8742,43 +8742,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AE174"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.6640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="54.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.69921875" style="38" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69921875" style="38" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.19921875" style="38" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.19921875" style="38" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.19921875" style="38" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.69921875" style="38" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="54.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.296875" style="38" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" style="38" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" style="38" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.83203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.796875" style="38" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" style="2" customWidth="1"/>
-    <col min="23" max="23" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11" style="2" customWidth="1"/>
     <col min="25" max="25" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11" style="2" customWidth="1"/>
-    <col min="27" max="27" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.296875" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" style="2" customWidth="1"/>
-    <col min="29" max="29" width="7.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" style="2" customWidth="1"/>
     <col min="31" max="31" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="32" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>189</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -8968,7 +8968,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -10108,7 +10108,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>16</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>17</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>18</v>
       </c>
@@ -10488,7 +10488,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>19</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>20</v>
       </c>
@@ -10678,7 +10678,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>21</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>22</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>23</v>
       </c>
@@ -10963,7 +10963,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>24</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>25</v>
       </c>
@@ -11153,7 +11153,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>26</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>27</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>28</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>29</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>30</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>31</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>32</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>33</v>
       </c>
@@ -11913,7 +11913,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>34</v>
       </c>
@@ -12008,7 +12008,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>35</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>36</v>
       </c>
@@ -12198,7 +12198,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>37</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>38</v>
       </c>
@@ -12388,7 +12388,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>39</v>
       </c>
@@ -12483,7 +12483,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>40</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>41</v>
       </c>
@@ -12673,7 +12673,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>42</v>
       </c>
@@ -12768,7 +12768,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>43</v>
       </c>
@@ -12863,7 +12863,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>44</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>45</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>46</v>
       </c>
@@ -13148,7 +13148,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>47</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>48</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>49</v>
       </c>
@@ -13433,7 +13433,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>50</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>51</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>52</v>
       </c>
@@ -13718,7 +13718,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>53</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>54</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>55</v>
       </c>
@@ -14003,7 +14003,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>56</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>57</v>
       </c>
@@ -14193,7 +14193,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>58</v>
       </c>
@@ -14288,7 +14288,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>59</v>
       </c>
@@ -14383,7 +14383,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>60</v>
       </c>
@@ -14478,7 +14478,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>61</v>
       </c>
@@ -14573,7 +14573,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="62" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>62</v>
       </c>
@@ -14668,7 +14668,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="63" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>63</v>
       </c>
@@ -14763,7 +14763,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <v>64</v>
       </c>
@@ -14858,7 +14858,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>65</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>66</v>
       </c>
@@ -15048,7 +15048,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <v>67</v>
       </c>
@@ -15143,7 +15143,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>68</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>69</v>
       </c>
@@ -15333,7 +15333,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>70</v>
       </c>
@@ -15428,7 +15428,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>71</v>
       </c>
@@ -15523,7 +15523,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>72</v>
       </c>
@@ -15618,7 +15618,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>73</v>
       </c>
@@ -15713,7 +15713,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>74</v>
       </c>
@@ -15808,7 +15808,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>75</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>76</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>77</v>
       </c>
@@ -16093,7 +16093,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>78</v>
       </c>
@@ -16188,7 +16188,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>79</v>
       </c>
@@ -16283,7 +16283,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <v>80</v>
       </c>
@@ -16378,7 +16378,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="81" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>81</v>
       </c>
@@ -16473,7 +16473,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="82" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <v>82</v>
       </c>
@@ -16568,7 +16568,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="83" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <v>83</v>
       </c>
@@ -16663,7 +16663,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="84" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>84</v>
       </c>
@@ -16758,7 +16758,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="85" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>85</v>
       </c>
@@ -16853,7 +16853,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="86" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>86</v>
       </c>
@@ -16948,7 +16948,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="87" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>87</v>
       </c>
@@ -17043,7 +17043,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="88" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>88</v>
       </c>
@@ -17138,7 +17138,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="89" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>89</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="90" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>90</v>
       </c>
@@ -17328,7 +17328,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="91" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>91</v>
       </c>
@@ -17423,7 +17423,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="92" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
         <v>92</v>
       </c>
@@ -17518,7 +17518,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="93" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <v>93</v>
       </c>
@@ -17613,7 +17613,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="94" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
         <v>94</v>
       </c>
@@ -17708,7 +17708,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="95" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
         <v>95</v>
       </c>
@@ -17803,7 +17803,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="96" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
         <v>96</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="97" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
         <v>97</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="98" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
         <v>98</v>
       </c>
@@ -18088,7 +18088,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="99" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
         <v>99</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="100" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
         <v>100</v>
       </c>
@@ -18278,7 +18278,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="101" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
         <v>101</v>
       </c>
@@ -18373,7 +18373,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="102" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
         <v>102</v>
       </c>
@@ -18468,7 +18468,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="103" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
         <v>103</v>
       </c>
@@ -18563,7 +18563,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="104" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
         <v>104</v>
       </c>
@@ -18658,7 +18658,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="105" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
         <v>105</v>
       </c>
@@ -18753,7 +18753,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="106" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
         <v>106</v>
       </c>
@@ -18848,7 +18848,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="107" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
         <v>107</v>
       </c>
@@ -18943,7 +18943,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="108" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
         <v>108</v>
       </c>
@@ -19038,7 +19038,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="109" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
         <v>109</v>
       </c>
@@ -19133,7 +19133,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="110" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
         <v>110</v>
       </c>
@@ -19228,7 +19228,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="111" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
         <v>111</v>
       </c>
@@ -19323,7 +19323,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="112" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8">
         <v>112</v>
       </c>
@@ -19418,7 +19418,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="113" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
         <v>113</v>
       </c>
@@ -19513,7 +19513,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="114" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8">
         <v>114</v>
       </c>
@@ -19608,7 +19608,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="115" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
         <v>115</v>
       </c>
@@ -19703,7 +19703,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="116" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="8">
         <v>116</v>
       </c>
@@ -19798,7 +19798,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="117" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
         <v>117</v>
       </c>
@@ -19893,7 +19893,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="118" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
         <v>118</v>
       </c>
@@ -19988,7 +19988,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="119" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
         <v>119</v>
       </c>
@@ -20083,7 +20083,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="120" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <v>120</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="121" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
         <v>121</v>
       </c>
@@ -20273,7 +20273,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="122" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
         <v>122</v>
       </c>
@@ -20368,7 +20368,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="123" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
         <v>123</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="124" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
         <v>124</v>
       </c>
@@ -20558,7 +20558,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="125" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
         <v>125</v>
       </c>
@@ -20653,7 +20653,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="126" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="8">
         <v>126</v>
       </c>
@@ -20748,7 +20748,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="127" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <v>127</v>
       </c>
@@ -20843,7 +20843,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="128" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
         <v>128</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="129" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <v>129</v>
       </c>
@@ -21033,7 +21033,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="8">
         <v>130</v>
       </c>
@@ -21128,7 +21128,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <v>131</v>
       </c>
@@ -21223,7 +21223,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
         <v>132</v>
       </c>
@@ -21318,7 +21318,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <v>133</v>
       </c>
@@ -21413,7 +21413,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="134" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
         <v>134</v>
       </c>
@@ -21508,7 +21508,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <v>135</v>
       </c>
@@ -21603,7 +21603,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
         <v>136</v>
       </c>
@@ -21698,7 +21698,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="137" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <v>137</v>
       </c>
@@ -21793,7 +21793,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="138" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
         <v>138</v>
       </c>
@@ -21888,7 +21888,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="139" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <v>139</v>
       </c>
@@ -21983,7 +21983,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
         <v>140</v>
       </c>
@@ -22078,7 +22078,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <v>141</v>
       </c>
@@ -22173,7 +22173,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
         <v>142</v>
       </c>
@@ -22268,7 +22268,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <v>143</v>
       </c>
@@ -22363,7 +22363,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
         <v>144</v>
       </c>
@@ -22458,7 +22458,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <v>145</v>
       </c>
@@ -22553,7 +22553,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
         <v>146</v>
       </c>
@@ -22648,7 +22648,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <v>147</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
         <v>148</v>
       </c>
@@ -22838,7 +22838,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <v>149</v>
       </c>
@@ -22933,7 +22933,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
         <v>150</v>
       </c>
@@ -23028,7 +23028,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <v>151</v>
       </c>
@@ -23123,7 +23123,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
         <v>152</v>
       </c>
@@ -23218,7 +23218,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <v>153</v>
       </c>
@@ -23313,7 +23313,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
         <v>154</v>
       </c>
@@ -23408,7 +23408,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
         <v>155</v>
       </c>
@@ -23503,7 +23503,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
         <v>156</v>
       </c>
@@ -23598,7 +23598,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
         <v>157</v>
       </c>
@@ -23693,7 +23693,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
         <v>158</v>
       </c>
@@ -23788,7 +23788,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
         <v>159</v>
       </c>
@@ -23883,7 +23883,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
         <v>160</v>
       </c>
@@ -23978,7 +23978,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="161" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
         <v>161</v>
       </c>
@@ -24073,7 +24073,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="162" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
         <v>162</v>
       </c>
@@ -24168,7 +24168,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="163" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
         <v>163</v>
       </c>
@@ -24263,7 +24263,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="164" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
         <v>164</v>
       </c>
@@ -24358,7 +24358,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="165" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <v>165</v>
       </c>
@@ -24453,7 +24453,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="166" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <v>166</v>
       </c>
@@ -24548,7 +24548,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="167" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <v>166</v>
       </c>
@@ -24643,7 +24643,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="168" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
         <v>166</v>
       </c>
@@ -24738,7 +24738,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="169" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:31" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
         <v>166</v>
       </c>
@@ -24833,7 +24833,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="170" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="8">
         <v>167</v>
       </c>
@@ -24929,7 +24929,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="171" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="8">
         <v>168</v>
       </c>
@@ -25025,7 +25025,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="172" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="8">
         <v>169</v>
       </c>
@@ -25121,7 +25121,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="173" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="8">
         <v>170</v>
       </c>
@@ -25217,7 +25217,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="174" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="8">
         <v>171</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A40F36A-9330-4E5C-963D-15D5628357F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC13033E-913A-45F6-B25A-A904A3C5501B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5922" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5949" uniqueCount="654">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2050,6 +2050,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2700,313 +2703,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="149">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="113">
     <dxf>
       <font>
         <b val="0"/>
@@ -3385,6 +3082,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -5796,39 +5501,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AE174" headerRowCount="0" totalsRowShown="0" headerRowDxfId="148" dataDxfId="146" headerRowBorderDxfId="147" tableBorderDxfId="145" totalsRowBorderDxfId="144">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AE174" headerRowCount="0" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109" totalsRowBorderDxfId="108">
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="143" dataDxfId="142"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="141" dataDxfId="140"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="139" dataDxfId="138"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="137" dataDxfId="136"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="135" dataDxfId="134"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="133" dataDxfId="132"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="131" dataDxfId="130"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="129" dataDxfId="128"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="127" dataDxfId="126"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="125" dataDxfId="124"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="123" dataDxfId="122"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="121" dataDxfId="120"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="119" dataDxfId="118"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="117" dataDxfId="116"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="115" dataDxfId="114"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="113" dataDxfId="112"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="111" dataDxfId="110"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="109" dataDxfId="108"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="107" dataDxfId="106"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="105" dataDxfId="104"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="103" dataDxfId="102"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="101" dataDxfId="100"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="99" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{67BF49D0-5BD9-4C65-9F7F-321F877F93D3}" name="Coluna22" headerRowDxfId="97" dataDxfId="96"/>
-    <tableColumn id="27" xr3:uid="{7A57466B-85C9-4F19-B457-DD53AF8B8B43}" name="Coluna23" headerRowDxfId="95" dataDxfId="94"/>
-    <tableColumn id="28" xr3:uid="{6D0F7AE3-FE22-4AE0-AE3D-EA7C26DBB834}" name="Coluna24" headerRowDxfId="93" dataDxfId="92"/>
-    <tableColumn id="29" xr3:uid="{B5303D9A-769C-4D11-ADE2-1AAE03620B1A}" name="Coluna25" headerRowDxfId="91" dataDxfId="90"/>
-    <tableColumn id="30" xr3:uid="{4F8D4348-881E-4EAD-A52A-10BC46F48D0D}" name="Coluna26" headerRowDxfId="89" dataDxfId="88"/>
-    <tableColumn id="31" xr3:uid="{C0E47BB3-37C7-4FBB-B9CB-C678EBFDA4CA}" name="Coluna27" headerRowDxfId="87" dataDxfId="86"/>
-    <tableColumn id="32" xr3:uid="{6015C5FC-5AAA-4A27-A4C7-2E5CBBCB9787}" name="Coluna28" headerRowDxfId="85" dataDxfId="84"/>
-    <tableColumn id="33" xr3:uid="{ECDE8196-C351-4A04-9C91-30718C7DA362}" name="Coluna29" headerRowDxfId="83" dataDxfId="82"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="107" dataDxfId="106"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="105" dataDxfId="104"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="103" dataDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="101" dataDxfId="100"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="99" dataDxfId="98"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="97" dataDxfId="96"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="95" dataDxfId="94"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="93" dataDxfId="92"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="91" dataDxfId="90"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="89" dataDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="87" dataDxfId="86"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="85" dataDxfId="84"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="83" dataDxfId="82"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="81" dataDxfId="80"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="79" dataDxfId="78"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="77" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="75" dataDxfId="74"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{67BF49D0-5BD9-4C65-9F7F-321F877F93D3}" name="Coluna22" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="27" xr3:uid="{7A57466B-85C9-4F19-B457-DD53AF8B8B43}" name="Coluna23" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="28" xr3:uid="{6D0F7AE3-FE22-4AE0-AE3D-EA7C26DBB834}" name="Coluna24" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="29" xr3:uid="{B5303D9A-769C-4D11-ADE2-1AAE03620B1A}" name="Coluna25" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="30" xr3:uid="{4F8D4348-881E-4EAD-A52A-10BC46F48D0D}" name="Coluna26" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="31" xr3:uid="{C0E47BB3-37C7-4FBB-B9CB-C678EBFDA4CA}" name="Coluna27" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="32" xr3:uid="{6015C5FC-5AAA-4A27-A4C7-2E5CBBCB9787}" name="Coluna28" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="33" xr3:uid="{ECDE8196-C351-4A04-9C91-30718C7DA362}" name="Coluna29" headerRowDxfId="47" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -6355,7 +6060,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46268.492902199076</v>
+        <v>46268.687518865743</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
@@ -6609,7 +6314,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75533AB-3BC5-4EED-85BC-780B8F4A6EA8}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AD27"/>
   <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
@@ -6635,10 +6340,10 @@
     <col min="25" max="25" width="42.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="8" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="57.75" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>374</v>
       </c>
@@ -6726,8 +6431,11 @@
       <c r="AC1" s="23" t="s">
         <v>397</v>
       </c>
+      <c r="AD1" s="23" t="s">
+        <v>653</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="55">
         <v>2</v>
       </c>
@@ -6823,8 +6531,11 @@
       <c r="AC2" s="42" t="s">
         <v>446</v>
       </c>
+      <c r="AD2" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="55">
         <v>3</v>
       </c>
@@ -6920,8 +6631,11 @@
       <c r="AC3" s="42" t="s">
         <v>447</v>
       </c>
+      <c r="AD3" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="55">
         <v>4</v>
       </c>
@@ -7017,8 +6731,11 @@
       <c r="AC4" s="42" t="s">
         <v>448</v>
       </c>
+      <c r="AD4" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="55">
         <v>5</v>
       </c>
@@ -7114,8 +6831,11 @@
       <c r="AC5" s="42" t="s">
         <v>369</v>
       </c>
+      <c r="AD5" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="55">
         <v>6</v>
       </c>
@@ -7211,8 +6931,11 @@
       <c r="AC6" s="42" t="s">
         <v>449</v>
       </c>
+      <c r="AD6" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="55">
         <v>7</v>
       </c>
@@ -7308,8 +7031,11 @@
       <c r="AC7" s="42" t="s">
         <v>450</v>
       </c>
+      <c r="AD7" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="55">
         <v>8</v>
       </c>
@@ -7405,8 +7131,11 @@
       <c r="AC8" s="42" t="s">
         <v>451</v>
       </c>
+      <c r="AD8" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="55">
         <v>9</v>
       </c>
@@ -7502,8 +7231,11 @@
       <c r="AC9" s="42" t="s">
         <v>452</v>
       </c>
+      <c r="AD9" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="55">
         <v>10</v>
       </c>
@@ -7599,8 +7331,11 @@
       <c r="AC10" s="42" t="s">
         <v>453</v>
       </c>
+      <c r="AD10" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="55">
         <v>11</v>
       </c>
@@ -7696,8 +7431,11 @@
       <c r="AC11" s="42" t="s">
         <v>454</v>
       </c>
+      <c r="AD11" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="55">
         <v>12</v>
       </c>
@@ -7793,8 +7531,11 @@
       <c r="AC12" s="42" t="s">
         <v>455</v>
       </c>
+      <c r="AD12" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="55">
         <v>13</v>
       </c>
@@ -7890,8 +7631,11 @@
       <c r="AC13" s="42" t="s">
         <v>456</v>
       </c>
+      <c r="AD13" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="55">
         <v>14</v>
       </c>
@@ -7987,8 +7731,11 @@
       <c r="AC14" s="42" t="s">
         <v>457</v>
       </c>
+      <c r="AD14" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="55">
         <v>15</v>
       </c>
@@ -8084,8 +7831,11 @@
       <c r="AC15" s="59" t="s">
         <v>496</v>
       </c>
+      <c r="AD15" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="55">
         <v>16</v>
       </c>
@@ -8181,8 +7931,11 @@
       <c r="AC16" s="59" t="s">
         <v>497</v>
       </c>
+      <c r="AD16" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="55">
         <v>17</v>
       </c>
@@ -8278,8 +8031,11 @@
       <c r="AC17" s="59" t="s">
         <v>498</v>
       </c>
+      <c r="AD17" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="55">
         <v>18</v>
       </c>
@@ -8375,8 +8131,11 @@
       <c r="AC18" s="59" t="s">
         <v>499</v>
       </c>
+      <c r="AD18" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="55">
         <v>19</v>
       </c>
@@ -8472,8 +8231,11 @@
       <c r="AC19" s="59" t="s">
         <v>503</v>
       </c>
+      <c r="AD19" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="55">
         <v>20</v>
       </c>
@@ -8569,8 +8331,11 @@
       <c r="AC20" s="59" t="s">
         <v>500</v>
       </c>
+      <c r="AD20" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="55">
         <v>21</v>
       </c>
@@ -8666,8 +8431,11 @@
       <c r="AC21" s="59" t="s">
         <v>501</v>
       </c>
+      <c r="AD21" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="55">
         <v>22</v>
       </c>
@@ -8763,8 +8531,11 @@
       <c r="AC22" s="59" t="s">
         <v>502</v>
       </c>
+      <c r="AD22" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="55">
         <v>23</v>
       </c>
@@ -8860,8 +8631,11 @@
       <c r="AC23" s="75" t="s">
         <v>191</v>
       </c>
+      <c r="AD23" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="55">
         <v>24</v>
       </c>
@@ -8957,8 +8731,11 @@
       <c r="AC24" s="75" t="s">
         <v>191</v>
       </c>
+      <c r="AD24" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="55">
         <v>25</v>
       </c>
@@ -9054,8 +8831,11 @@
       <c r="AC25" s="75" t="s">
         <v>191</v>
       </c>
+      <c r="AD25" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="55">
         <v>26</v>
       </c>
@@ -9151,8 +8931,11 @@
       <c r="AC26" s="75" t="s">
         <v>191</v>
       </c>
+      <c r="AD26" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="55">
         <v>27</v>
       </c>
@@ -9248,35 +9031,38 @@
       <c r="AC27" s="75" t="s">
         <v>191</v>
       </c>
+      <c r="AD27" s="75" t="s">
+        <v>191</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B27">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:F27">
-    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="80" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="79" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F26">
-    <cfRule type="duplicateValues" dxfId="75" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R22">
-    <cfRule type="cellIs" dxfId="74" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="73" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9429,7 +9215,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="72" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9474,7 +9260,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26060,164 +25846,164 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B169 B175:B1048576">
-    <cfRule type="duplicateValues" dxfId="70" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170:B174">
-    <cfRule type="duplicateValues" dxfId="69" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="67" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E170:E174">
-    <cfRule type="cellIs" dxfId="66" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="65" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="64" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F170:F174">
-    <cfRule type="cellIs" dxfId="64" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G170:G174">
-    <cfRule type="cellIs" dxfId="63" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="62" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H170:H174">
-    <cfRule type="cellIs" dxfId="61" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I170:I174">
-    <cfRule type="cellIs" dxfId="60" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="59" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="62" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="58" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="53" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="57" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="68" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="56" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="55" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="59" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R170:U174">
-    <cfRule type="cellIs" dxfId="54" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="49" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="53" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:U169">
-    <cfRule type="cellIs" dxfId="52" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:AE1 D170:D174 T175:AE1048576">
-    <cfRule type="cellIs" dxfId="51" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="31" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="50" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="56" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:W174">
-    <cfRule type="cellIs" dxfId="49" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="48" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X174">
-    <cfRule type="cellIs" dxfId="47" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y174">
-    <cfRule type="cellIs" dxfId="46" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="45" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z174">
-    <cfRule type="cellIs" dxfId="44" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA174">
-    <cfRule type="cellIs" dxfId="43" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB174">
-    <cfRule type="cellIs" dxfId="41" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC174">
-    <cfRule type="cellIs" dxfId="40" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD174">
-    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE174">
-    <cfRule type="cellIs" dxfId="37" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC13033E-913A-45F6-B25A-A904A3C5501B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B079B7A8-8435-4601-AFBD-4B9A181DE0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5949" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5984" uniqueCount="665">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1911,18 +1911,6 @@
     <t>Atributo Ifc</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -2037,9 +2025,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -2053,6 +2038,54 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>API Método</t>
+  </si>
+  <si>
+    <t>Função Auxiliar</t>
+  </si>
+  <si>
+    <t>API Plataforma</t>
+  </si>
+  <si>
+    <t>API Macros</t>
+  </si>
+  <si>
+    <t>Função Global</t>
+  </si>
+  <si>
+    <t>Função Local</t>
+  </si>
+  <si>
+    <t>Função Filtro</t>
+  </si>
+  <si>
+    <t>API Método Visual</t>
+  </si>
+  <si>
+    <t>Bloco de Código</t>
+  </si>
+  <si>
+    <t>API Macros Visuais</t>
   </si>
 </sst>
 </file>
@@ -2454,7 +2487,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2697,13 +2730,86 @@
     <xf numFmtId="0" fontId="8" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="113">
+  <dxfs count="119">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3082,14 +3188,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -5501,39 +5599,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AE174" headerRowCount="0" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109" totalsRowBorderDxfId="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AE174" headerRowCount="0" totalsRowShown="0" headerRowDxfId="118" dataDxfId="116" headerRowBorderDxfId="117" tableBorderDxfId="115" totalsRowBorderDxfId="114">
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="107" dataDxfId="106"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="105" dataDxfId="104"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="103" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="101" dataDxfId="100"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="99" dataDxfId="98"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="97" dataDxfId="96"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="95" dataDxfId="94"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="93" dataDxfId="92"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="91" dataDxfId="90"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="89" dataDxfId="88"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="87" dataDxfId="86"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="85" dataDxfId="84"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="83" dataDxfId="82"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="81" dataDxfId="80"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="79" dataDxfId="78"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="77" dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="75" dataDxfId="74"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="73" dataDxfId="72"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="71" dataDxfId="70"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{67BF49D0-5BD9-4C65-9F7F-321F877F93D3}" name="Coluna22" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="27" xr3:uid="{7A57466B-85C9-4F19-B457-DD53AF8B8B43}" name="Coluna23" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="28" xr3:uid="{6D0F7AE3-FE22-4AE0-AE3D-EA7C26DBB834}" name="Coluna24" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="29" xr3:uid="{B5303D9A-769C-4D11-ADE2-1AAE03620B1A}" name="Coluna25" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="30" xr3:uid="{4F8D4348-881E-4EAD-A52A-10BC46F48D0D}" name="Coluna26" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="31" xr3:uid="{C0E47BB3-37C7-4FBB-B9CB-C678EBFDA4CA}" name="Coluna27" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="32" xr3:uid="{6015C5FC-5AAA-4A27-A4C7-2E5CBBCB9787}" name="Coluna28" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="33" xr3:uid="{ECDE8196-C351-4A04-9C91-30718C7DA362}" name="Coluna29" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="113" dataDxfId="112"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="111" dataDxfId="110"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="109" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="107" dataDxfId="106"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="105" dataDxfId="104"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="103" dataDxfId="102"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="101" dataDxfId="100"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="99" dataDxfId="98"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="97" dataDxfId="96"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="95" dataDxfId="94"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="93" dataDxfId="92"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="91" dataDxfId="90"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="89" dataDxfId="88"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="87" dataDxfId="86"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="85" dataDxfId="84"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="83" dataDxfId="82"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="81" dataDxfId="80"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="79" dataDxfId="78"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="77" dataDxfId="76"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="75" dataDxfId="74"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{67BF49D0-5BD9-4C65-9F7F-321F877F93D3}" name="Coluna22" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="27" xr3:uid="{7A57466B-85C9-4F19-B457-DD53AF8B8B43}" name="Coluna23" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="28" xr3:uid="{6D0F7AE3-FE22-4AE0-AE3D-EA7C26DBB834}" name="Coluna24" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="29" xr3:uid="{B5303D9A-769C-4D11-ADE2-1AAE03620B1A}" name="Coluna25" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="30" xr3:uid="{4F8D4348-881E-4EAD-A52A-10BC46F48D0D}" name="Coluna26" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="31" xr3:uid="{C0E47BB3-37C7-4FBB-B9CB-C678EBFDA4CA}" name="Coluna27" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="32" xr3:uid="{6015C5FC-5AAA-4A27-A4C7-2E5CBBCB9787}" name="Coluna28" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="33" xr3:uid="{ECDE8196-C351-4A04-9C91-30718C7DA362}" name="Coluna29" headerRowDxfId="53" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -6060,7 +6158,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46268.687518865743</v>
+        <v>46273.465192476855</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
@@ -6331,7 +6429,7 @@
     <col min="16" max="16" width="60" customWidth="1"/>
     <col min="17" max="17" width="63.5" customWidth="1"/>
     <col min="18" max="18" width="53.5" customWidth="1"/>
-    <col min="19" max="19" width="5" style="33" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5" style="86" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
@@ -6398,7 +6496,7 @@
       <c r="R1" s="41" t="s">
         <v>427</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="S1" s="24" t="s">
         <v>418</v>
       </c>
       <c r="T1" s="23" t="s">
@@ -6432,7 +6530,7 @@
         <v>397</v>
       </c>
       <c r="AD1" s="23" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6494,7 +6592,7 @@
       <c r="R2" s="60" t="s">
         <v>511</v>
       </c>
-      <c r="S2" s="42" t="s">
+      <c r="S2" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T2" s="59" t="str">
@@ -6594,7 +6692,7 @@
       <c r="R3" s="60" t="s">
         <v>514</v>
       </c>
-      <c r="S3" s="42" t="s">
+      <c r="S3" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T3" s="59" t="str">
@@ -6694,7 +6792,7 @@
       <c r="R4" s="60" t="s">
         <v>517</v>
       </c>
-      <c r="S4" s="42" t="s">
+      <c r="S4" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T4" s="59" t="str">
@@ -6794,7 +6892,7 @@
       <c r="R5" s="60" t="s">
         <v>520</v>
       </c>
-      <c r="S5" s="42" t="s">
+      <c r="S5" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T5" s="59" t="str">
@@ -6894,7 +6992,7 @@
       <c r="R6" s="60" t="s">
         <v>523</v>
       </c>
-      <c r="S6" s="42" t="s">
+      <c r="S6" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T6" s="59" t="str">
@@ -6994,7 +7092,7 @@
       <c r="R7" s="60" t="s">
         <v>526</v>
       </c>
-      <c r="S7" s="42" t="s">
+      <c r="S7" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T7" s="59" t="str">
@@ -7094,7 +7192,7 @@
       <c r="R8" s="60" t="s">
         <v>529</v>
       </c>
-      <c r="S8" s="42" t="s">
+      <c r="S8" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T8" s="59" t="str">
@@ -7194,7 +7292,7 @@
       <c r="R9" s="60" t="s">
         <v>532</v>
       </c>
-      <c r="S9" s="42" t="s">
+      <c r="S9" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T9" s="59" t="str">
@@ -7294,7 +7392,7 @@
       <c r="R10" s="60" t="s">
         <v>535</v>
       </c>
-      <c r="S10" s="42" t="s">
+      <c r="S10" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T10" s="59" t="str">
@@ -7394,7 +7492,7 @@
       <c r="R11" s="60" t="s">
         <v>538</v>
       </c>
-      <c r="S11" s="42" t="s">
+      <c r="S11" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T11" s="59" t="str">
@@ -7494,7 +7592,7 @@
       <c r="R12" s="60" t="s">
         <v>541</v>
       </c>
-      <c r="S12" s="42" t="s">
+      <c r="S12" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T12" s="59" t="str">
@@ -7594,7 +7692,7 @@
       <c r="R13" s="60" t="s">
         <v>544</v>
       </c>
-      <c r="S13" s="42" t="s">
+      <c r="S13" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T13" s="59" t="str">
@@ -7694,7 +7792,7 @@
       <c r="R14" s="60" t="s">
         <v>547</v>
       </c>
-      <c r="S14" s="42" t="s">
+      <c r="S14" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T14" s="59" t="str">
@@ -7770,7 +7868,7 @@
         <v>191</v>
       </c>
       <c r="L15" s="58" t="str">
-        <f t="shared" ref="L15:N22" si="4">CONCATENATE("", C15)</f>
+        <f t="shared" ref="L15:N27" si="4">CONCATENATE("", C15)</f>
         <v>Normativos</v>
       </c>
       <c r="M15" s="58" t="str">
@@ -7794,7 +7892,7 @@
       <c r="R15" s="42" t="s">
         <v>588</v>
       </c>
-      <c r="S15" s="42" t="s">
+      <c r="S15" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T15" s="59" t="str">
@@ -7894,7 +7992,7 @@
       <c r="R16" s="42" t="s">
         <v>589</v>
       </c>
-      <c r="S16" s="42" t="s">
+      <c r="S16" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T16" s="59" t="str">
@@ -7994,7 +8092,7 @@
       <c r="R17" s="42" t="s">
         <v>590</v>
       </c>
-      <c r="S17" s="42" t="s">
+      <c r="S17" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T17" s="59" t="str">
@@ -8094,7 +8192,7 @@
       <c r="R18" s="42" t="s">
         <v>591</v>
       </c>
-      <c r="S18" s="42" t="s">
+      <c r="S18" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T18" s="59" t="str">
@@ -8194,7 +8292,7 @@
       <c r="R19" s="42" t="s">
         <v>592</v>
       </c>
-      <c r="S19" s="42" t="s">
+      <c r="S19" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T19" s="59" t="str">
@@ -8294,7 +8392,7 @@
       <c r="R20" s="42" t="s">
         <v>593</v>
       </c>
-      <c r="S20" s="42" t="s">
+      <c r="S20" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T20" s="59" t="str">
@@ -8394,7 +8492,7 @@
       <c r="R21" s="42" t="s">
         <v>594</v>
       </c>
-      <c r="S21" s="42" t="s">
+      <c r="S21" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T21" s="59" t="str">
@@ -8494,7 +8592,7 @@
       <c r="R22" s="42" t="s">
         <v>595</v>
       </c>
-      <c r="S22" s="42" t="s">
+      <c r="S22" s="84" t="s">
         <v>191</v>
       </c>
       <c r="T22" s="59" t="str">
@@ -8535,24 +8633,24 @@
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" s="85" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="55">
         <v>23</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>606</v>
+        <v>649</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>609</v>
+        <v>651</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>191</v>
@@ -8569,45 +8667,38 @@
       <c r="K23" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="L23" s="58" t="str">
-        <f t="shared" ref="L23:O27" si="9">SUBSTITUTE(CONCATENATE("", C23), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M23" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N23" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O23" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Função Auxiliar</v>
+      <c r="L23" s="58" t="s">
+        <v>650</v>
+      </c>
+      <c r="M23" s="58" t="s">
+        <v>651</v>
+      </c>
+      <c r="N23" s="58" t="s">
+        <v>655</v>
+      </c>
+      <c r="O23" s="58" t="s">
+        <v>656</v>
       </c>
       <c r="P23" s="42" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="Q23" s="42" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="R23" s="42" t="s">
-        <v>635</v>
-      </c>
-      <c r="S23" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="T23" s="42" t="str">
-        <f t="shared" ref="T23:V27" si="10">SUBSTITUTE(C23, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U23" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V23" s="59" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>631</v>
+      </c>
+      <c r="S23" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="T23" s="42" t="s">
+        <v>657</v>
+      </c>
+      <c r="U23" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="V23" s="59" t="s">
+        <v>655</v>
       </c>
       <c r="W23" s="42" t="s">
         <v>445</v>
@@ -8635,24 +8726,24 @@
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" s="85" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="55">
         <v>24</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>606</v>
+        <v>649</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>609</v>
+        <v>651</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="F24" s="32" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>191</v>
@@ -8669,45 +8760,38 @@
       <c r="K24" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="L24" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>De API</v>
-      </c>
-      <c r="M24" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N24" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O24" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Função Global</v>
+      <c r="L24" s="58" t="s">
+        <v>650</v>
+      </c>
+      <c r="M24" s="58" t="s">
+        <v>651</v>
+      </c>
+      <c r="N24" s="58" t="s">
+        <v>655</v>
+      </c>
+      <c r="O24" s="58" t="s">
+        <v>659</v>
       </c>
       <c r="P24" s="42" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="Q24" s="42" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="R24" s="42" t="s">
-        <v>639</v>
-      </c>
-      <c r="S24" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="T24" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="U24" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V24" s="59" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>635</v>
+      </c>
+      <c r="S24" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="T24" s="42" t="s">
+        <v>657</v>
+      </c>
+      <c r="U24" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="V24" s="59" t="s">
+        <v>655</v>
       </c>
       <c r="W24" s="42" t="s">
         <v>445</v>
@@ -8735,24 +8819,24 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" s="85" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="55">
         <v>25</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>606</v>
+        <v>649</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>609</v>
+        <v>651</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>191</v>
@@ -8769,45 +8853,38 @@
       <c r="K25" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="L25" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>De API</v>
-      </c>
-      <c r="M25" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N25" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O25" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Função Local</v>
+      <c r="L25" s="58" t="s">
+        <v>650</v>
+      </c>
+      <c r="M25" s="58" t="s">
+        <v>651</v>
+      </c>
+      <c r="N25" s="58" t="s">
+        <v>655</v>
+      </c>
+      <c r="O25" s="58" t="s">
+        <v>660</v>
       </c>
       <c r="P25" s="42" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="Q25" s="42" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="R25" s="42" t="s">
-        <v>643</v>
-      </c>
-      <c r="S25" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="T25" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="U25" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V25" s="59" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>639</v>
+      </c>
+      <c r="S25" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="T25" s="42" t="s">
+        <v>657</v>
+      </c>
+      <c r="U25" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="V25" s="59" t="s">
+        <v>655</v>
       </c>
       <c r="W25" s="42" t="s">
         <v>445</v>
@@ -8835,24 +8912,24 @@
         <v>191</v>
       </c>
     </row>
-    <row r="26" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" s="85" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="55">
         <v>26</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>606</v>
+        <v>649</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>609</v>
+        <v>651</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="F26" s="32" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>191</v>
@@ -8869,45 +8946,38 @@
       <c r="K26" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="L26" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>De API</v>
-      </c>
-      <c r="M26" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N26" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O26" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Função Filtro</v>
+      <c r="L26" s="58" t="s">
+        <v>650</v>
+      </c>
+      <c r="M26" s="58" t="s">
+        <v>651</v>
+      </c>
+      <c r="N26" s="58" t="s">
+        <v>655</v>
+      </c>
+      <c r="O26" s="58" t="s">
+        <v>661</v>
       </c>
       <c r="P26" s="42" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="Q26" s="42" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="R26" s="42" t="s">
-        <v>647</v>
-      </c>
-      <c r="S26" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="T26" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="U26" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V26" s="59" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>643</v>
+      </c>
+      <c r="S26" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="T26" s="42" t="s">
+        <v>657</v>
+      </c>
+      <c r="U26" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="V26" s="59" t="s">
+        <v>655</v>
       </c>
       <c r="W26" s="42" t="s">
         <v>445</v>
@@ -8935,24 +9005,24 @@
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="1:30" s="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" s="85" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="55">
         <v>27</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>606</v>
+        <v>649</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="G27" s="35" t="s">
         <v>191</v>
@@ -8969,45 +9039,38 @@
       <c r="K27" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="L27" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>De API</v>
-      </c>
-      <c r="M27" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N27" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O27" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v>Bloco de Código</v>
+      <c r="L27" s="58" t="s">
+        <v>650</v>
+      </c>
+      <c r="M27" s="58" t="s">
+        <v>653</v>
+      </c>
+      <c r="N27" s="58" t="s">
+        <v>662</v>
+      </c>
+      <c r="O27" s="58" t="s">
+        <v>663</v>
       </c>
       <c r="P27" s="42" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="Q27" s="42" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="R27" s="42" t="s">
-        <v>652</v>
-      </c>
-      <c r="S27" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="T27" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="U27" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V27" s="59" t="str">
-        <f t="shared" si="10"/>
-        <v>Códigos Visuais</v>
+        <v>647</v>
+      </c>
+      <c r="S27" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="T27" s="42" t="s">
+        <v>657</v>
+      </c>
+      <c r="U27" s="42" t="s">
+        <v>664</v>
+      </c>
+      <c r="V27" s="59" t="s">
+        <v>662</v>
       </c>
       <c r="W27" s="42" t="s">
         <v>445</v>
@@ -9036,35 +9099,35 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B27">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B22 A23:A27">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E27:F27">
-    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="43" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="42" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23:F26">
-    <cfRule type="duplicateValues" dxfId="38" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R22">
-    <cfRule type="cellIs" dxfId="37" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="36" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F27">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F27">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -9215,7 +9278,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9260,7 +9323,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9658,34 +9721,34 @@
         <v>191</v>
       </c>
       <c r="V4" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W4" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X4" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y4" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X4" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y4" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z4" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA4" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB4" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC4" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD4" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE4" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -9753,34 +9816,34 @@
         <v>191</v>
       </c>
       <c r="V5" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W5" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X5" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y5" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X5" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y5" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z5" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA5" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB5" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC5" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD5" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE5" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -9848,34 +9911,34 @@
         <v>191</v>
       </c>
       <c r="V6" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W6" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X6" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y6" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X6" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y6" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z6" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA6" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB6" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC6" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD6" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE6" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -9943,34 +10006,34 @@
         <v>191</v>
       </c>
       <c r="V7" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W7" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X7" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y7" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X7" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y7" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z7" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA7" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB7" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC7" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD7" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE7" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10038,34 +10101,34 @@
         <v>191</v>
       </c>
       <c r="V8" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W8" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X8" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y8" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X8" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y8" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z8" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA8" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB8" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC8" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD8" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE8" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10133,34 +10196,34 @@
         <v>191</v>
       </c>
       <c r="V9" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W9" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X9" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y9" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X9" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y9" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z9" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA9" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB9" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC9" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD9" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE9" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10228,34 +10291,34 @@
         <v>191</v>
       </c>
       <c r="V10" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W10" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X10" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y10" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X10" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y10" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z10" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA10" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB10" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC10" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD10" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE10" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10323,34 +10386,34 @@
         <v>191</v>
       </c>
       <c r="V11" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W11" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X11" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y11" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X11" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y11" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z11" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA11" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB11" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC11" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD11" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE11" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10418,34 +10481,34 @@
         <v>191</v>
       </c>
       <c r="V12" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W12" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X12" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y12" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X12" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y12" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z12" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA12" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB12" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC12" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD12" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE12" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10513,34 +10576,34 @@
         <v>191</v>
       </c>
       <c r="V13" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W13" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X13" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y13" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X13" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y13" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z13" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA13" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB13" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC13" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD13" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE13" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10608,34 +10671,34 @@
         <v>191</v>
       </c>
       <c r="V14" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W14" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X14" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y14" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X14" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y14" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z14" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA14" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB14" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC14" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD14" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE14" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10703,34 +10766,34 @@
         <v>191</v>
       </c>
       <c r="V15" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W15" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X15" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y15" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X15" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y15" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z15" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA15" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB15" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC15" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD15" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE15" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10798,34 +10861,34 @@
         <v>191</v>
       </c>
       <c r="V16" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W16" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X16" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y16" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X16" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y16" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z16" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA16" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB16" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC16" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD16" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE16" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10893,34 +10956,34 @@
         <v>191</v>
       </c>
       <c r="V17" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W17" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X17" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y17" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X17" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y17" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z17" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA17" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB17" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC17" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD17" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE17" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10988,34 +11051,34 @@
         <v>191</v>
       </c>
       <c r="V18" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W18" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X18" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y18" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X18" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y18" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z18" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA18" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB18" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC18" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD18" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE18" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11083,34 +11146,34 @@
         <v>191</v>
       </c>
       <c r="V19" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W19" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X19" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y19" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X19" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y19" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z19" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA19" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB19" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC19" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD19" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE19" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11178,34 +11241,34 @@
         <v>191</v>
       </c>
       <c r="V20" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W20" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X20" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y20" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X20" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y20" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z20" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA20" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB20" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC20" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD20" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE20" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11273,34 +11336,34 @@
         <v>191</v>
       </c>
       <c r="V21" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W21" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X21" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y21" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X21" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y21" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z21" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA21" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB21" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC21" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD21" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE21" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11368,34 +11431,34 @@
         <v>191</v>
       </c>
       <c r="V22" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W22" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X22" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y22" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X22" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y22" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z22" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA22" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB22" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC22" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD22" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE22" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11463,34 +11526,34 @@
         <v>191</v>
       </c>
       <c r="V23" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W23" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X23" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y23" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X23" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y23" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z23" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA23" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB23" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC23" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD23" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE23" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11558,34 +11621,34 @@
         <v>191</v>
       </c>
       <c r="V24" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W24" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X24" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y24" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X24" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y24" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z24" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA24" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB24" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC24" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD24" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE24" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11653,34 +11716,34 @@
         <v>191</v>
       </c>
       <c r="V25" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W25" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X25" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y25" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X25" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y25" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z25" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA25" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB25" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC25" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD25" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE25" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11748,34 +11811,34 @@
         <v>191</v>
       </c>
       <c r="V26" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W26" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X26" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y26" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X26" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y26" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z26" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA26" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB26" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC26" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD26" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE26" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11843,34 +11906,34 @@
         <v>191</v>
       </c>
       <c r="V27" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W27" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X27" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y27" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X27" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y27" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z27" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA27" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB27" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC27" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD27" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE27" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11938,34 +12001,34 @@
         <v>191</v>
       </c>
       <c r="V28" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W28" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X28" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y28" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X28" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y28" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z28" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA28" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB28" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC28" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD28" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE28" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12033,34 +12096,34 @@
         <v>191</v>
       </c>
       <c r="V29" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W29" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X29" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y29" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X29" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y29" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z29" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA29" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB29" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC29" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD29" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE29" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12128,34 +12191,34 @@
         <v>191</v>
       </c>
       <c r="V30" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W30" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X30" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y30" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X30" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y30" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z30" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA30" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB30" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC30" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD30" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE30" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12223,34 +12286,34 @@
         <v>191</v>
       </c>
       <c r="V31" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W31" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X31" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y31" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X31" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y31" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z31" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA31" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB31" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC31" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD31" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE31" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12318,34 +12381,34 @@
         <v>191</v>
       </c>
       <c r="V32" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W32" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X32" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y32" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X32" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y32" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z32" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA32" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB32" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC32" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD32" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE32" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12413,34 +12476,34 @@
         <v>191</v>
       </c>
       <c r="V33" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W33" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X33" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y33" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X33" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y33" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z33" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA33" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB33" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC33" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD33" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE33" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12508,34 +12571,34 @@
         <v>191</v>
       </c>
       <c r="V34" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W34" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X34" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y34" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X34" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y34" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z34" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA34" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB34" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC34" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD34" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE34" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12603,34 +12666,34 @@
         <v>191</v>
       </c>
       <c r="V35" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W35" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X35" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y35" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X35" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y35" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z35" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA35" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB35" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC35" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD35" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE35" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12698,34 +12761,34 @@
         <v>191</v>
       </c>
       <c r="V36" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W36" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X36" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y36" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X36" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y36" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z36" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA36" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB36" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC36" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD36" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE36" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12793,34 +12856,34 @@
         <v>191</v>
       </c>
       <c r="V37" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W37" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X37" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y37" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X37" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y37" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z37" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA37" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB37" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC37" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD37" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE37" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12888,34 +12951,34 @@
         <v>191</v>
       </c>
       <c r="V38" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W38" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X38" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y38" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X38" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y38" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z38" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA38" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB38" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC38" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD38" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE38" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12983,34 +13046,34 @@
         <v>191</v>
       </c>
       <c r="V39" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W39" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X39" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y39" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X39" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y39" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z39" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA39" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB39" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC39" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD39" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE39" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="40" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13078,34 +13141,34 @@
         <v>191</v>
       </c>
       <c r="V40" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W40" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X40" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y40" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X40" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y40" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z40" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA40" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB40" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC40" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD40" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE40" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="41" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13173,34 +13236,34 @@
         <v>191</v>
       </c>
       <c r="V41" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W41" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X41" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y41" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X41" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y41" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z41" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA41" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB41" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC41" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD41" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE41" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="42" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13268,34 +13331,34 @@
         <v>191</v>
       </c>
       <c r="V42" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W42" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X42" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y42" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X42" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y42" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z42" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA42" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB42" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC42" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD42" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE42" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="43" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13363,34 +13426,34 @@
         <v>191</v>
       </c>
       <c r="V43" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W43" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X43" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y43" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X43" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y43" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z43" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA43" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB43" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC43" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD43" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE43" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="44" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13458,34 +13521,34 @@
         <v>191</v>
       </c>
       <c r="V44" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W44" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X44" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y44" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X44" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y44" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z44" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA44" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB44" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC44" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD44" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE44" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13553,34 +13616,34 @@
         <v>191</v>
       </c>
       <c r="V45" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W45" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X45" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y45" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X45" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y45" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z45" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA45" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB45" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC45" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD45" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE45" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="46" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13648,34 +13711,34 @@
         <v>191</v>
       </c>
       <c r="V46" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W46" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X46" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y46" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X46" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y46" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z46" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA46" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB46" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC46" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD46" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE46" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="47" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13743,34 +13806,34 @@
         <v>191</v>
       </c>
       <c r="V47" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W47" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X47" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y47" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X47" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y47" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z47" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA47" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB47" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC47" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD47" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE47" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="48" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13838,34 +13901,34 @@
         <v>191</v>
       </c>
       <c r="V48" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W48" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X48" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y48" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X48" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y48" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z48" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA48" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB48" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC48" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD48" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE48" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="49" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13933,34 +13996,34 @@
         <v>191</v>
       </c>
       <c r="V49" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W49" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X49" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y49" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X49" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y49" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z49" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA49" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB49" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC49" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD49" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE49" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="50" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14028,34 +14091,34 @@
         <v>191</v>
       </c>
       <c r="V50" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W50" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X50" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y50" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X50" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y50" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z50" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA50" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB50" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC50" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD50" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE50" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="51" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14123,34 +14186,34 @@
         <v>191</v>
       </c>
       <c r="V51" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W51" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X51" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y51" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X51" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y51" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z51" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA51" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB51" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC51" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD51" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE51" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="52" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14218,34 +14281,34 @@
         <v>191</v>
       </c>
       <c r="V52" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W52" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X52" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y52" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X52" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y52" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z52" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA52" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB52" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC52" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD52" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE52" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="53" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14313,34 +14376,34 @@
         <v>191</v>
       </c>
       <c r="V53" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W53" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X53" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y53" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X53" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y53" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z53" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA53" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB53" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC53" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD53" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE53" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="54" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14408,34 +14471,34 @@
         <v>191</v>
       </c>
       <c r="V54" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W54" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X54" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y54" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X54" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y54" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z54" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA54" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB54" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC54" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD54" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE54" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="55" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14503,34 +14566,34 @@
         <v>191</v>
       </c>
       <c r="V55" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W55" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X55" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y55" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X55" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y55" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z55" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA55" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB55" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC55" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD55" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE55" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="56" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14598,34 +14661,34 @@
         <v>191</v>
       </c>
       <c r="V56" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W56" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X56" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y56" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X56" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y56" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z56" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA56" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB56" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC56" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD56" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE56" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="57" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14693,34 +14756,34 @@
         <v>191</v>
       </c>
       <c r="V57" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W57" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X57" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y57" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X57" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y57" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z57" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA57" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB57" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC57" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD57" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE57" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="58" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14788,34 +14851,34 @@
         <v>191</v>
       </c>
       <c r="V58" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W58" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X58" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y58" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X58" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y58" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z58" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA58" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB58" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC58" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD58" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE58" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="59" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14883,34 +14946,34 @@
         <v>191</v>
       </c>
       <c r="V59" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W59" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X59" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y59" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X59" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y59" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z59" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA59" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB59" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC59" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD59" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE59" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="60" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14978,34 +15041,34 @@
         <v>191</v>
       </c>
       <c r="V60" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W60" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X60" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y60" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X60" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y60" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z60" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA60" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB60" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC60" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD60" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE60" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="61" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15073,34 +15136,34 @@
         <v>191</v>
       </c>
       <c r="V61" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W61" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X61" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y61" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X61" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y61" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z61" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA61" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB61" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC61" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD61" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE61" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="62" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15168,34 +15231,34 @@
         <v>191</v>
       </c>
       <c r="V62" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W62" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X62" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y62" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X62" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y62" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z62" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA62" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB62" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC62" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD62" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE62" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="63" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15263,34 +15326,34 @@
         <v>191</v>
       </c>
       <c r="V63" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W63" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X63" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y63" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X63" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y63" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z63" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA63" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB63" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC63" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD63" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE63" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="64" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15358,34 +15421,34 @@
         <v>191</v>
       </c>
       <c r="V64" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W64" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X64" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y64" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X64" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y64" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z64" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA64" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB64" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC64" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD64" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE64" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="65" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15453,34 +15516,34 @@
         <v>191</v>
       </c>
       <c r="V65" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W65" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X65" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y65" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X65" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y65" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z65" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA65" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB65" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC65" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD65" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE65" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="66" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15548,34 +15611,34 @@
         <v>191</v>
       </c>
       <c r="V66" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W66" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X66" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y66" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X66" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y66" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z66" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA66" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB66" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC66" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD66" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE66" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="67" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15643,34 +15706,34 @@
         <v>191</v>
       </c>
       <c r="V67" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W67" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X67" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y67" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X67" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y67" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z67" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA67" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB67" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC67" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD67" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE67" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="68" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15738,34 +15801,34 @@
         <v>191</v>
       </c>
       <c r="V68" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W68" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X68" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y68" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X68" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y68" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z68" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA68" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB68" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC68" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD68" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE68" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="69" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15833,34 +15896,34 @@
         <v>191</v>
       </c>
       <c r="V69" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W69" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X69" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y69" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X69" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y69" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z69" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA69" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB69" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC69" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD69" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE69" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="70" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15928,34 +15991,34 @@
         <v>191</v>
       </c>
       <c r="V70" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W70" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X70" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y70" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X70" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y70" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z70" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA70" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB70" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC70" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD70" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE70" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="71" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16023,34 +16086,34 @@
         <v>191</v>
       </c>
       <c r="V71" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W71" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X71" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y71" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X71" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y71" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z71" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA71" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB71" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC71" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD71" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE71" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="72" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16118,34 +16181,34 @@
         <v>191</v>
       </c>
       <c r="V72" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W72" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X72" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y72" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X72" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y72" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z72" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA72" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB72" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC72" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD72" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE72" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="73" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16213,34 +16276,34 @@
         <v>191</v>
       </c>
       <c r="V73" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W73" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X73" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y73" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X73" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y73" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z73" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA73" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB73" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC73" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD73" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE73" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="74" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16308,34 +16371,34 @@
         <v>191</v>
       </c>
       <c r="V74" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W74" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X74" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y74" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X74" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y74" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z74" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA74" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB74" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC74" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD74" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE74" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="75" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16403,34 +16466,34 @@
         <v>191</v>
       </c>
       <c r="V75" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W75" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X75" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y75" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X75" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y75" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z75" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA75" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB75" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC75" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD75" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE75" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="76" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16498,34 +16561,34 @@
         <v>191</v>
       </c>
       <c r="V76" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W76" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X76" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y76" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X76" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y76" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z76" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA76" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB76" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC76" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD76" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE76" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="77" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16593,34 +16656,34 @@
         <v>191</v>
       </c>
       <c r="V77" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W77" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X77" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y77" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X77" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y77" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z77" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA77" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB77" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC77" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD77" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE77" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="78" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16688,34 +16751,34 @@
         <v>191</v>
       </c>
       <c r="V78" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W78" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X78" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y78" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X78" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y78" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z78" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA78" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB78" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC78" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD78" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE78" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="79" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16783,34 +16846,34 @@
         <v>191</v>
       </c>
       <c r="V79" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W79" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X79" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y79" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X79" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y79" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z79" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA79" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB79" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC79" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD79" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE79" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="80" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16878,34 +16941,34 @@
         <v>191</v>
       </c>
       <c r="V80" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W80" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X80" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y80" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X80" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y80" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z80" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA80" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB80" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC80" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD80" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE80" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="81" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16973,34 +17036,34 @@
         <v>191</v>
       </c>
       <c r="V81" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W81" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X81" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y81" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X81" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y81" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z81" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA81" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB81" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC81" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD81" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE81" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="82" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17068,34 +17131,34 @@
         <v>191</v>
       </c>
       <c r="V82" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W82" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X82" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y82" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X82" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y82" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z82" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA82" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB82" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC82" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD82" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE82" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="83" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17163,34 +17226,34 @@
         <v>191</v>
       </c>
       <c r="V83" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W83" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X83" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y83" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X83" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y83" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z83" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA83" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB83" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC83" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD83" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE83" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="84" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17258,34 +17321,34 @@
         <v>191</v>
       </c>
       <c r="V84" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W84" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X84" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y84" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X84" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y84" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z84" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA84" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB84" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC84" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD84" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE84" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="85" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17353,34 +17416,34 @@
         <v>191</v>
       </c>
       <c r="V85" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W85" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X85" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y85" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X85" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y85" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z85" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA85" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB85" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC85" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD85" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE85" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="86" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17448,34 +17511,34 @@
         <v>191</v>
       </c>
       <c r="V86" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W86" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X86" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y86" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X86" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y86" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z86" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA86" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB86" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC86" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD86" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE86" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="87" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17543,34 +17606,34 @@
         <v>191</v>
       </c>
       <c r="V87" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W87" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X87" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y87" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X87" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y87" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z87" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA87" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB87" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC87" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD87" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE87" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="88" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17638,34 +17701,34 @@
         <v>191</v>
       </c>
       <c r="V88" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W88" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X88" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y88" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X88" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y88" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z88" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA88" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB88" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC88" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD88" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE88" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="89" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17733,34 +17796,34 @@
         <v>191</v>
       </c>
       <c r="V89" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W89" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X89" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y89" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X89" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y89" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z89" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA89" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB89" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC89" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD89" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE89" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="90" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17828,34 +17891,34 @@
         <v>191</v>
       </c>
       <c r="V90" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W90" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X90" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y90" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X90" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y90" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z90" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA90" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB90" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC90" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD90" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE90" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="91" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17923,34 +17986,34 @@
         <v>191</v>
       </c>
       <c r="V91" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W91" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X91" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y91" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X91" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y91" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z91" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA91" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB91" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC91" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD91" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE91" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="92" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18018,34 +18081,34 @@
         <v>191</v>
       </c>
       <c r="V92" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W92" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X92" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y92" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X92" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y92" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z92" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA92" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB92" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC92" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD92" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE92" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="93" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18113,34 +18176,34 @@
         <v>191</v>
       </c>
       <c r="V93" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W93" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X93" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y93" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X93" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y93" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z93" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA93" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB93" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC93" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD93" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE93" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="94" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18208,34 +18271,34 @@
         <v>191</v>
       </c>
       <c r="V94" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W94" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X94" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y94" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X94" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y94" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z94" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA94" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB94" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC94" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD94" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE94" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="95" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18303,34 +18366,34 @@
         <v>191</v>
       </c>
       <c r="V95" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W95" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X95" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y95" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X95" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y95" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z95" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA95" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB95" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC95" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD95" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE95" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="96" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18398,34 +18461,34 @@
         <v>191</v>
       </c>
       <c r="V96" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W96" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X96" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y96" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X96" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y96" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z96" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA96" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB96" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC96" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD96" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE96" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="97" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18493,34 +18556,34 @@
         <v>191</v>
       </c>
       <c r="V97" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W97" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X97" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y97" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X97" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y97" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z97" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA97" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB97" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC97" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD97" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE97" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="98" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18588,34 +18651,34 @@
         <v>191</v>
       </c>
       <c r="V98" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W98" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X98" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y98" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X98" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y98" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z98" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA98" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB98" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC98" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD98" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE98" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="99" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18683,34 +18746,34 @@
         <v>191</v>
       </c>
       <c r="V99" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W99" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X99" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y99" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X99" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y99" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z99" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA99" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB99" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC99" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD99" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE99" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="100" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18778,34 +18841,34 @@
         <v>191</v>
       </c>
       <c r="V100" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W100" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X100" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y100" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X100" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y100" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z100" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA100" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB100" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC100" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD100" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE100" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="101" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18873,34 +18936,34 @@
         <v>191</v>
       </c>
       <c r="V101" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W101" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X101" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y101" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X101" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y101" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z101" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA101" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB101" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC101" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD101" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE101" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="102" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18968,34 +19031,34 @@
         <v>191</v>
       </c>
       <c r="V102" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W102" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X102" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y102" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X102" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y102" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z102" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA102" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB102" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC102" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD102" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE102" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="103" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19063,34 +19126,34 @@
         <v>191</v>
       </c>
       <c r="V103" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W103" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X103" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y103" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X103" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y103" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z103" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA103" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB103" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC103" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD103" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE103" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="104" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19158,34 +19221,34 @@
         <v>191</v>
       </c>
       <c r="V104" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W104" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X104" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y104" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X104" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y104" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z104" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA104" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB104" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC104" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD104" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE104" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="105" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19253,34 +19316,34 @@
         <v>191</v>
       </c>
       <c r="V105" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W105" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X105" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y105" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X105" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y105" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z105" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA105" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB105" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC105" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD105" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE105" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="106" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19348,34 +19411,34 @@
         <v>191</v>
       </c>
       <c r="V106" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W106" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X106" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y106" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X106" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y106" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z106" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA106" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB106" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC106" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD106" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE106" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="107" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19443,34 +19506,34 @@
         <v>191</v>
       </c>
       <c r="V107" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W107" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X107" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y107" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X107" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y107" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z107" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA107" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB107" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC107" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD107" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE107" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="108" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19538,34 +19601,34 @@
         <v>191</v>
       </c>
       <c r="V108" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W108" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X108" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y108" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X108" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y108" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z108" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA108" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB108" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC108" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD108" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE108" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="109" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19633,34 +19696,34 @@
         <v>191</v>
       </c>
       <c r="V109" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W109" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X109" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y109" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X109" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y109" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z109" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA109" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB109" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC109" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD109" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE109" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="110" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19728,34 +19791,34 @@
         <v>191</v>
       </c>
       <c r="V110" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W110" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X110" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y110" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X110" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y110" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z110" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA110" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB110" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC110" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD110" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE110" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="111" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19823,34 +19886,34 @@
         <v>191</v>
       </c>
       <c r="V111" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W111" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X111" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y111" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X111" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y111" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z111" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA111" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB111" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC111" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD111" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE111" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="112" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19918,34 +19981,34 @@
         <v>191</v>
       </c>
       <c r="V112" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W112" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X112" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y112" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X112" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y112" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z112" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA112" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB112" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC112" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD112" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE112" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="113" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20013,34 +20076,34 @@
         <v>191</v>
       </c>
       <c r="V113" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W113" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X113" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y113" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X113" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y113" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z113" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA113" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB113" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC113" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD113" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE113" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="114" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20108,34 +20171,34 @@
         <v>191</v>
       </c>
       <c r="V114" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W114" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X114" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y114" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X114" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y114" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z114" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA114" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB114" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC114" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD114" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE114" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="115" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20203,34 +20266,34 @@
         <v>191</v>
       </c>
       <c r="V115" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W115" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X115" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y115" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X115" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y115" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z115" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA115" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB115" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC115" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD115" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE115" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="116" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20298,34 +20361,34 @@
         <v>191</v>
       </c>
       <c r="V116" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W116" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X116" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y116" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X116" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y116" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z116" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA116" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB116" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC116" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD116" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE116" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="117" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20393,34 +20456,34 @@
         <v>191</v>
       </c>
       <c r="V117" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W117" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X117" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y117" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X117" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y117" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z117" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA117" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB117" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC117" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD117" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE117" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="118" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20488,34 +20551,34 @@
         <v>191</v>
       </c>
       <c r="V118" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W118" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X118" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y118" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X118" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y118" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z118" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA118" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB118" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC118" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD118" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE118" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="119" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20583,34 +20646,34 @@
         <v>191</v>
       </c>
       <c r="V119" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W119" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X119" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y119" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X119" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y119" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z119" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA119" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB119" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC119" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD119" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE119" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="120" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20678,34 +20741,34 @@
         <v>191</v>
       </c>
       <c r="V120" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W120" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X120" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y120" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X120" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y120" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z120" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA120" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB120" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC120" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD120" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE120" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="121" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20773,34 +20836,34 @@
         <v>191</v>
       </c>
       <c r="V121" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W121" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X121" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y121" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X121" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y121" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z121" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA121" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB121" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC121" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD121" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE121" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="122" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20868,34 +20931,34 @@
         <v>191</v>
       </c>
       <c r="V122" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W122" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X122" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y122" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X122" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y122" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z122" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA122" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB122" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC122" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD122" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE122" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="123" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20963,34 +21026,34 @@
         <v>191</v>
       </c>
       <c r="V123" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W123" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X123" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y123" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X123" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y123" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z123" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA123" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB123" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC123" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD123" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE123" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="124" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21058,34 +21121,34 @@
         <v>191</v>
       </c>
       <c r="V124" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W124" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X124" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y124" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X124" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y124" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z124" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA124" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB124" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC124" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD124" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE124" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="125" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21153,34 +21216,34 @@
         <v>191</v>
       </c>
       <c r="V125" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W125" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X125" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y125" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X125" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y125" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z125" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA125" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB125" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC125" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD125" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE125" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="126" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21248,34 +21311,34 @@
         <v>191</v>
       </c>
       <c r="V126" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W126" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X126" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y126" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X126" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y126" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z126" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA126" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB126" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC126" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD126" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE126" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="127" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21343,34 +21406,34 @@
         <v>191</v>
       </c>
       <c r="V127" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W127" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X127" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y127" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X127" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y127" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z127" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA127" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB127" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC127" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD127" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE127" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="128" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21438,34 +21501,34 @@
         <v>191</v>
       </c>
       <c r="V128" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W128" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X128" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y128" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X128" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y128" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z128" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA128" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB128" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC128" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD128" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE128" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="129" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21533,34 +21596,34 @@
         <v>191</v>
       </c>
       <c r="V129" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W129" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X129" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y129" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X129" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y129" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z129" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA129" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB129" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC129" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD129" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE129" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="130" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21628,34 +21691,34 @@
         <v>191</v>
       </c>
       <c r="V130" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W130" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X130" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y130" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X130" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y130" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z130" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA130" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB130" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC130" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD130" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE130" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="131" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21723,34 +21786,34 @@
         <v>191</v>
       </c>
       <c r="V131" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W131" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X131" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y131" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X131" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y131" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z131" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA131" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB131" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC131" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD131" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE131" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="132" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21818,34 +21881,34 @@
         <v>191</v>
       </c>
       <c r="V132" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W132" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X132" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y132" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X132" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y132" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z132" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA132" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB132" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC132" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD132" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE132" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="133" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21913,34 +21976,34 @@
         <v>191</v>
       </c>
       <c r="V133" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W133" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X133" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y133" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X133" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y133" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z133" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA133" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB133" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC133" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD133" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE133" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="134" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22008,34 +22071,34 @@
         <v>191</v>
       </c>
       <c r="V134" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W134" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X134" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y134" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X134" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y134" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z134" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA134" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB134" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC134" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD134" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE134" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="135" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22103,34 +22166,34 @@
         <v>191</v>
       </c>
       <c r="V135" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W135" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X135" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y135" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X135" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y135" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z135" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA135" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB135" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC135" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD135" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE135" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="136" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22198,34 +22261,34 @@
         <v>191</v>
       </c>
       <c r="V136" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W136" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X136" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y136" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X136" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y136" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z136" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA136" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB136" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC136" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD136" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE136" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="137" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22293,34 +22356,34 @@
         <v>191</v>
       </c>
       <c r="V137" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W137" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X137" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y137" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X137" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y137" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z137" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA137" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB137" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC137" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD137" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE137" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="138" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22388,34 +22451,34 @@
         <v>191</v>
       </c>
       <c r="V138" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W138" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X138" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y138" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X138" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y138" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z138" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA138" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB138" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC138" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD138" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE138" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="139" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22483,34 +22546,34 @@
         <v>191</v>
       </c>
       <c r="V139" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W139" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X139" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y139" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X139" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y139" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z139" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA139" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB139" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC139" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD139" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE139" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="140" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22578,34 +22641,34 @@
         <v>191</v>
       </c>
       <c r="V140" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W140" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X140" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y140" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X140" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y140" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z140" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA140" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB140" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC140" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD140" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE140" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="141" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22673,34 +22736,34 @@
         <v>191</v>
       </c>
       <c r="V141" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W141" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X141" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y141" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X141" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y141" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z141" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA141" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB141" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC141" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD141" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE141" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="142" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22768,34 +22831,34 @@
         <v>191</v>
       </c>
       <c r="V142" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W142" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X142" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y142" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X142" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y142" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z142" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA142" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB142" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC142" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD142" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE142" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="143" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22863,34 +22926,34 @@
         <v>191</v>
       </c>
       <c r="V143" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W143" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X143" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y143" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X143" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y143" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z143" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA143" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB143" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC143" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD143" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE143" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="144" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22958,34 +23021,34 @@
         <v>191</v>
       </c>
       <c r="V144" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W144" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X144" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y144" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X144" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y144" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z144" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA144" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB144" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC144" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD144" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE144" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="145" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23053,34 +23116,34 @@
         <v>191</v>
       </c>
       <c r="V145" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W145" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X145" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y145" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X145" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y145" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z145" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA145" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB145" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC145" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD145" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE145" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="146" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23148,34 +23211,34 @@
         <v>191</v>
       </c>
       <c r="V146" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W146" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X146" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y146" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X146" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y146" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z146" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA146" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB146" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC146" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD146" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE146" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="147" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23243,34 +23306,34 @@
         <v>191</v>
       </c>
       <c r="V147" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W147" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X147" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y147" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X147" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y147" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z147" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA147" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB147" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC147" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD147" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE147" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="148" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23338,34 +23401,34 @@
         <v>191</v>
       </c>
       <c r="V148" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W148" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X148" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y148" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X148" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y148" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z148" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA148" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB148" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC148" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD148" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE148" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="149" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23433,34 +23496,34 @@
         <v>191</v>
       </c>
       <c r="V149" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W149" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X149" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y149" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X149" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y149" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z149" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA149" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB149" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC149" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD149" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE149" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="150" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23528,34 +23591,34 @@
         <v>191</v>
       </c>
       <c r="V150" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W150" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X150" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y150" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X150" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y150" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z150" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA150" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB150" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC150" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD150" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE150" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="151" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23623,34 +23686,34 @@
         <v>191</v>
       </c>
       <c r="V151" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W151" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X151" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y151" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X151" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y151" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z151" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA151" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB151" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC151" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD151" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE151" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="152" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23718,34 +23781,34 @@
         <v>191</v>
       </c>
       <c r="V152" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W152" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X152" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y152" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X152" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y152" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z152" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA152" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB152" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC152" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD152" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE152" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="153" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23813,34 +23876,34 @@
         <v>191</v>
       </c>
       <c r="V153" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W153" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X153" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y153" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X153" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y153" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z153" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA153" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB153" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC153" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD153" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE153" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="154" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23908,34 +23971,34 @@
         <v>191</v>
       </c>
       <c r="V154" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W154" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X154" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y154" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X154" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y154" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z154" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA154" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB154" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC154" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD154" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE154" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="155" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24003,34 +24066,34 @@
         <v>191</v>
       </c>
       <c r="V155" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W155" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X155" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y155" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X155" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y155" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z155" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA155" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB155" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC155" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD155" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE155" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="156" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24098,34 +24161,34 @@
         <v>191</v>
       </c>
       <c r="V156" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W156" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X156" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y156" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X156" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y156" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z156" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA156" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB156" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC156" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD156" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE156" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="157" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24193,34 +24256,34 @@
         <v>191</v>
       </c>
       <c r="V157" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W157" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X157" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y157" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X157" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y157" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z157" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA157" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB157" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC157" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD157" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE157" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="158" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24288,34 +24351,34 @@
         <v>191</v>
       </c>
       <c r="V158" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W158" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X158" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y158" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X158" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y158" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z158" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA158" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB158" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC158" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD158" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE158" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="159" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24383,34 +24446,34 @@
         <v>191</v>
       </c>
       <c r="V159" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W159" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X159" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y159" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X159" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y159" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z159" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA159" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB159" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC159" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD159" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE159" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="160" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24478,34 +24541,34 @@
         <v>191</v>
       </c>
       <c r="V160" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W160" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X160" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y160" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X160" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y160" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z160" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA160" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB160" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC160" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD160" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE160" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="161" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24573,34 +24636,34 @@
         <v>191</v>
       </c>
       <c r="V161" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W161" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X161" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y161" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X161" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y161" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z161" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA161" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB161" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC161" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD161" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE161" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="162" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24668,34 +24731,34 @@
         <v>191</v>
       </c>
       <c r="V162" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W162" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X162" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y162" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X162" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y162" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z162" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA162" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB162" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC162" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD162" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE162" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="163" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24763,34 +24826,34 @@
         <v>191</v>
       </c>
       <c r="V163" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W163" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X163" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y163" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X163" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y163" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z163" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA163" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB163" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC163" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD163" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE163" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="164" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24858,34 +24921,34 @@
         <v>191</v>
       </c>
       <c r="V164" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W164" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X164" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y164" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X164" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y164" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z164" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA164" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB164" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC164" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD164" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE164" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="165" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24953,34 +25016,34 @@
         <v>191</v>
       </c>
       <c r="V165" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W165" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X165" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y165" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X165" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y165" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z165" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA165" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB165" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC165" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD165" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE165" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="166" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25048,34 +25111,34 @@
         <v>191</v>
       </c>
       <c r="V166" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W166" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X166" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y166" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X166" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y166" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z166" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA166" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB166" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC166" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD166" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE166" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="167" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25143,34 +25206,34 @@
         <v>191</v>
       </c>
       <c r="V167" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W167" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X167" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y167" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X167" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y167" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z167" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA167" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB167" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC167" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD167" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE167" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="168" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25238,34 +25301,34 @@
         <v>191</v>
       </c>
       <c r="V168" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W168" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X168" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y168" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X168" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y168" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z168" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA168" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB168" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC168" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD168" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE168" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="169" spans="1:31" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25333,34 +25396,34 @@
         <v>191</v>
       </c>
       <c r="V169" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W169" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X169" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y169" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X169" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y169" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z169" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA169" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB169" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC169" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD169" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE169" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="170" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25368,10 +25431,10 @@
         <v>167</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C170" s="32" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D170" s="80" t="s">
         <v>191</v>
@@ -25395,26 +25458,26 @@
         <v>366</v>
       </c>
       <c r="K170" s="39" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="L170" s="36" t="s">
         <v>422</v>
       </c>
       <c r="M170" s="37" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="N170" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O170" s="13" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="P170" s="82" t="str">
         <f t="shared" ref="P170:P174" si="0">IF(Q170="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q170" s="83" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="R170" s="80" t="s">
         <v>191</v>
@@ -25429,34 +25492,34 @@
         <v>191</v>
       </c>
       <c r="V170" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W170" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X170" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y170" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X170" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y170" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z170" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA170" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB170" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC170" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD170" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE170" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="171" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25464,10 +25527,10 @@
         <v>168</v>
       </c>
       <c r="B171" s="14" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C171" s="32" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D171" s="80" t="s">
         <v>191</v>
@@ -25491,26 +25554,26 @@
         <v>366</v>
       </c>
       <c r="K171" s="39" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="L171" s="36" t="s">
         <v>422</v>
       </c>
       <c r="M171" s="39" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="N171" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O171" s="13" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="P171" s="82" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q171" s="83" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="R171" s="80" t="s">
         <v>191</v>
@@ -25525,34 +25588,34 @@
         <v>191</v>
       </c>
       <c r="V171" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W171" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X171" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y171" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X171" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y171" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z171" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA171" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB171" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC171" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD171" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE171" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="172" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25560,10 +25623,10 @@
         <v>169</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C172" s="32" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D172" s="80" t="s">
         <v>191</v>
@@ -25587,26 +25650,26 @@
         <v>366</v>
       </c>
       <c r="K172" s="39" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="L172" s="36" t="s">
         <v>422</v>
       </c>
       <c r="M172" s="39" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="N172" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O172" s="13" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="P172" s="82" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q172" s="83" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="R172" s="80" t="s">
         <v>191</v>
@@ -25621,34 +25684,34 @@
         <v>191</v>
       </c>
       <c r="V172" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W172" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X172" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y172" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X172" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y172" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z172" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA172" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB172" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC172" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD172" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE172" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="173" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25656,10 +25719,10 @@
         <v>170</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C173" s="32" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D173" s="80" t="s">
         <v>191</v>
@@ -25683,26 +25746,26 @@
         <v>366</v>
       </c>
       <c r="K173" s="39" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="L173" s="36" t="s">
         <v>422</v>
       </c>
       <c r="M173" s="39" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="N173" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O173" s="13" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="P173" s="82" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q173" s="83" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="R173" s="80" t="s">
         <v>191</v>
@@ -25717,34 +25780,34 @@
         <v>191</v>
       </c>
       <c r="V173" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W173" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X173" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y173" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X173" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y173" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z173" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA173" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB173" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC173" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD173" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE173" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="174" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25752,10 +25815,10 @@
         <v>171</v>
       </c>
       <c r="B174" s="79" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C174" s="32" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D174" s="81" t="s">
         <v>191</v>
@@ -25779,26 +25842,26 @@
         <v>366</v>
       </c>
       <c r="K174" s="78" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="L174" s="40" t="s">
         <v>422</v>
       </c>
       <c r="M174" s="78" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="N174" s="40" t="s">
         <v>1</v>
       </c>
       <c r="O174" s="19" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="P174" s="82" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q174" s="83" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="R174" s="81" t="s">
         <v>191</v>
@@ -25813,197 +25876,197 @@
         <v>191</v>
       </c>
       <c r="V174" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="W174" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="X174" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y174" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="X174" s="61" t="s">
-        <v>626</v>
-      </c>
-      <c r="Y174" s="62" t="s">
-        <v>614</v>
-      </c>
       <c r="Z174" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA174" s="62" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AB174" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AC174" s="62" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AD174" s="61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AE174" s="62" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B169 B175:B1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170:B174">
-    <cfRule type="duplicateValues" dxfId="32" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="30" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E170:E174">
-    <cfRule type="cellIs" dxfId="29" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="28" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="64" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F170:F174">
-    <cfRule type="cellIs" dxfId="27" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G170:G174">
-    <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="27" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="25" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H170:H174">
-    <cfRule type="cellIs" dxfId="24" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I170:I174">
-    <cfRule type="cellIs" dxfId="23" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="22" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="62" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="21" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="53" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="20" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="68" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="19" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="18" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="59" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R170:U174">
-    <cfRule type="cellIs" dxfId="17" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="49" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="16" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:U169">
-    <cfRule type="cellIs" dxfId="15" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:AE1 D170:D174 T175:AE1048576">
-    <cfRule type="cellIs" dxfId="14" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="31" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="13" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="56" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:W174">
-    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X174">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y174">
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z174">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA174">
-    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB174">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC174">
-    <cfRule type="cellIs" dxfId="3" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD174">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE174">
-    <cfRule type="cellIs" dxfId="0" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
